--- a/expertreview ver_Motivational Quotes Dataset.xlsx
+++ b/expertreview ver_Motivational Quotes Dataset.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Iman Mysarah\Documents\iman\PART 6 DEGREE\FYP\Dataset\expert review\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Iman Mysarah\Documents\iman\PART 6 DEGREE\FYP\Dev\fequote_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E106A2D-9FD8-42ED-8790-8FFF76040E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEF09BBE-0B7A-4D74-AEE0-E7DDA95DFE67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="664" xr2:uid="{9E271287-F749-47AF-91B2-5FAAEA58710C}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Labelled with Emotion" sheetId="4" r:id="rId1"/>
     <sheet name="Unknown Emotion" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Labelled with Emotion'!$A$1:$O$812</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -29,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6773" uniqueCount="2303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6775" uniqueCount="2303">
   <si>
     <t>joy</t>
   </si>
@@ -7532,6 +7535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDE07E1A-985C-40A8-94C0-CAAB4BA87E43}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:O812"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7598,7 +7602,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
         <v>11</v>
       </c>
@@ -7641,7 +7645,7 @@
       <c r="N2" s="13"/>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>14</v>
       </c>
@@ -7684,7 +7688,7 @@
       <c r="N3" s="15"/>
       <c r="O3" s="22"/>
     </row>
-    <row r="4" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>18</v>
       </c>
@@ -7727,7 +7731,7 @@
       <c r="N4" s="13"/>
       <c r="O4" s="20"/>
     </row>
-    <row r="5" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="21" t="s">
         <v>20</v>
       </c>
@@ -7770,7 +7774,7 @@
       <c r="N5" s="15"/>
       <c r="O5" s="22"/>
     </row>
-    <row r="6" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>25</v>
       </c>
@@ -7813,7 +7817,7 @@
       <c r="N6" s="13"/>
       <c r="O6" s="20"/>
     </row>
-    <row r="7" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="21" t="s">
         <v>31</v>
       </c>
@@ -7858,7 +7862,7 @@
       </c>
       <c r="O7" s="22"/>
     </row>
-    <row r="8" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
         <v>33</v>
       </c>
@@ -7901,7 +7905,7 @@
       <c r="N8" s="13"/>
       <c r="O8" s="20"/>
     </row>
-    <row r="9" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="21" t="s">
         <v>34</v>
       </c>
@@ -7944,7 +7948,7 @@
       <c r="N9" s="15"/>
       <c r="O9" s="22"/>
     </row>
-    <row r="10" spans="1:15" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="201.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
         <v>36</v>
       </c>
@@ -7987,7 +7991,7 @@
       <c r="N10" s="13"/>
       <c r="O10" s="20"/>
     </row>
-    <row r="11" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="21" t="s">
         <v>40</v>
       </c>
@@ -8030,7 +8034,7 @@
       <c r="N11" s="15"/>
       <c r="O11" s="22"/>
     </row>
-    <row r="12" spans="1:15" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="187.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
         <v>43</v>
       </c>
@@ -8073,7 +8077,7 @@
       <c r="N12" s="13"/>
       <c r="O12" s="20"/>
     </row>
-    <row r="13" spans="1:15" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="21" t="s">
         <v>45</v>
       </c>
@@ -8116,7 +8120,7 @@
       <c r="N13" s="15"/>
       <c r="O13" s="22"/>
     </row>
-    <row r="14" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
         <v>49</v>
       </c>
@@ -8161,7 +8165,7 @@
       </c>
       <c r="O14" s="20"/>
     </row>
-    <row r="15" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="21" t="s">
         <v>52</v>
       </c>
@@ -8206,7 +8210,7 @@
       </c>
       <c r="O15" s="22"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
         <v>56</v>
       </c>
@@ -8249,7 +8253,7 @@
       <c r="N16" s="13"/>
       <c r="O16" s="20"/>
     </row>
-    <row r="17" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="21" t="s">
         <v>60</v>
       </c>
@@ -8292,7 +8296,7 @@
       <c r="N17" s="15"/>
       <c r="O17" s="22"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
         <v>62</v>
       </c>
@@ -8335,7 +8339,7 @@
       <c r="N18" s="13"/>
       <c r="O18" s="20"/>
     </row>
-    <row r="19" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="21" t="s">
         <v>64</v>
       </c>
@@ -8380,7 +8384,7 @@
       </c>
       <c r="O19" s="22"/>
     </row>
-    <row r="20" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
         <v>65</v>
       </c>
@@ -8423,7 +8427,7 @@
       <c r="N20" s="13"/>
       <c r="O20" s="20"/>
     </row>
-    <row r="21" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="21" t="s">
         <v>69</v>
       </c>
@@ -8466,7 +8470,7 @@
       <c r="N21" s="15"/>
       <c r="O21" s="22"/>
     </row>
-    <row r="22" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
         <v>71</v>
       </c>
@@ -8511,7 +8515,7 @@
       </c>
       <c r="O22" s="20"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="21" t="s">
         <v>77</v>
       </c>
@@ -8554,7 +8558,7 @@
       <c r="N23" s="15"/>
       <c r="O23" s="22"/>
     </row>
-    <row r="24" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19" t="s">
         <v>79</v>
       </c>
@@ -8599,7 +8603,7 @@
       </c>
       <c r="O24" s="20"/>
     </row>
-    <row r="25" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="21" t="s">
         <v>84</v>
       </c>
@@ -8644,7 +8648,7 @@
       </c>
       <c r="O25" s="22"/>
     </row>
-    <row r="26" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="19" t="s">
         <v>87</v>
       </c>
@@ -8687,7 +8691,7 @@
       <c r="N26" s="13"/>
       <c r="O26" s="20"/>
     </row>
-    <row r="27" spans="1:15" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" ht="201.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="21" t="s">
         <v>91</v>
       </c>
@@ -8730,7 +8734,7 @@
       <c r="N27" s="15"/>
       <c r="O27" s="22"/>
     </row>
-    <row r="28" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="19" t="s">
         <v>94</v>
       </c>
@@ -8773,7 +8777,7 @@
       <c r="N28" s="13"/>
       <c r="O28" s="20"/>
     </row>
-    <row r="29" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="21" t="s">
         <v>96</v>
       </c>
@@ -8816,7 +8820,7 @@
       <c r="N29" s="15"/>
       <c r="O29" s="22"/>
     </row>
-    <row r="30" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="19" t="s">
         <v>98</v>
       </c>
@@ -8859,7 +8863,7 @@
       <c r="N30" s="13"/>
       <c r="O30" s="20"/>
     </row>
-    <row r="31" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="21" t="s">
         <v>100</v>
       </c>
@@ -8902,7 +8906,7 @@
       <c r="N31" s="15"/>
       <c r="O31" s="22"/>
     </row>
-    <row r="32" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="19" t="s">
         <v>102</v>
       </c>
@@ -8945,7 +8949,7 @@
       <c r="N32" s="13"/>
       <c r="O32" s="20"/>
     </row>
-    <row r="33" spans="1:15" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" ht="201.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="21" t="s">
         <v>103</v>
       </c>
@@ -8988,7 +8992,7 @@
       <c r="N33" s="15"/>
       <c r="O33" s="22"/>
     </row>
-    <row r="34" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="19" t="s">
         <v>109</v>
       </c>
@@ -9033,7 +9037,7 @@
       </c>
       <c r="O34" s="20"/>
     </row>
-    <row r="35" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="21" t="s">
         <v>112</v>
       </c>
@@ -9076,7 +9080,7 @@
       <c r="N35" s="15"/>
       <c r="O35" s="22"/>
     </row>
-    <row r="36" spans="1:15" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="19" t="s">
         <v>115</v>
       </c>
@@ -9121,7 +9125,7 @@
       </c>
       <c r="O36" s="20"/>
     </row>
-    <row r="37" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="21" t="s">
         <v>117</v>
       </c>
@@ -9164,7 +9168,7 @@
       <c r="N37" s="15"/>
       <c r="O37" s="22"/>
     </row>
-    <row r="38" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="19" t="s">
         <v>119</v>
       </c>
@@ -9209,7 +9213,7 @@
       </c>
       <c r="O38" s="20"/>
     </row>
-    <row r="39" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="21" t="s">
         <v>121</v>
       </c>
@@ -9252,7 +9256,7 @@
       <c r="N39" s="15"/>
       <c r="O39" s="22"/>
     </row>
-    <row r="40" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="19" t="s">
         <v>125</v>
       </c>
@@ -9295,7 +9299,7 @@
       <c r="N40" s="13"/>
       <c r="O40" s="20"/>
     </row>
-    <row r="41" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="21" t="s">
         <v>130</v>
       </c>
@@ -9340,7 +9344,7 @@
       </c>
       <c r="O41" s="22"/>
     </row>
-    <row r="42" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="19" t="s">
         <v>132</v>
       </c>
@@ -9383,7 +9387,7 @@
       <c r="N42" s="13"/>
       <c r="O42" s="20"/>
     </row>
-    <row r="43" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="21" t="s">
         <v>133</v>
       </c>
@@ -9426,7 +9430,7 @@
       <c r="N43" s="15"/>
       <c r="O43" s="22"/>
     </row>
-    <row r="44" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="19" t="s">
         <v>135</v>
       </c>
@@ -9469,7 +9473,7 @@
       <c r="N44" s="13"/>
       <c r="O44" s="20"/>
     </row>
-    <row r="45" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="21" t="s">
         <v>140</v>
       </c>
@@ -9512,7 +9516,7 @@
       <c r="N45" s="15"/>
       <c r="O45" s="22"/>
     </row>
-    <row r="46" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="19" t="s">
         <v>144</v>
       </c>
@@ -9555,7 +9559,7 @@
       <c r="N46" s="13"/>
       <c r="O46" s="20"/>
     </row>
-    <row r="47" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="21" t="s">
         <v>145</v>
       </c>
@@ -9598,7 +9602,7 @@
       <c r="N47" s="15"/>
       <c r="O47" s="22"/>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="19" t="s">
         <v>148</v>
       </c>
@@ -9641,7 +9645,7 @@
       <c r="N48" s="13"/>
       <c r="O48" s="20"/>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="21" t="s">
         <v>152</v>
       </c>
@@ -9684,7 +9688,7 @@
       <c r="N49" s="15"/>
       <c r="O49" s="22"/>
     </row>
-    <row r="50" spans="1:15" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="19" t="s">
         <v>155</v>
       </c>
@@ -9727,7 +9731,7 @@
       <c r="N50" s="13"/>
       <c r="O50" s="20"/>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="21" t="s">
         <v>160</v>
       </c>
@@ -9770,7 +9774,7 @@
       <c r="N51" s="15"/>
       <c r="O51" s="22"/>
     </row>
-    <row r="52" spans="1:15" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="19" t="s">
         <v>166</v>
       </c>
@@ -9813,7 +9817,7 @@
       <c r="N52" s="13"/>
       <c r="O52" s="20"/>
     </row>
-    <row r="53" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="21" t="s">
         <v>167</v>
       </c>
@@ -9856,7 +9860,7 @@
       <c r="N53" s="15"/>
       <c r="O53" s="22"/>
     </row>
-    <row r="54" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="19" t="s">
         <v>168</v>
       </c>
@@ -9899,7 +9903,7 @@
       <c r="N54" s="13"/>
       <c r="O54" s="20"/>
     </row>
-    <row r="55" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="21" t="s">
         <v>170</v>
       </c>
@@ -9942,7 +9946,7 @@
       <c r="N55" s="15"/>
       <c r="O55" s="22"/>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="19" t="s">
         <v>175</v>
       </c>
@@ -9985,7 +9989,7 @@
       <c r="N56" s="13"/>
       <c r="O56" s="20"/>
     </row>
-    <row r="57" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="21" t="s">
         <v>179</v>
       </c>
@@ -10028,7 +10032,7 @@
       <c r="N57" s="15"/>
       <c r="O57" s="22"/>
     </row>
-    <row r="58" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="19" t="s">
         <v>185</v>
       </c>
@@ -10071,7 +10075,7 @@
       <c r="N58" s="13"/>
       <c r="O58" s="20"/>
     </row>
-    <row r="59" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="21" t="s">
         <v>189</v>
       </c>
@@ -10114,7 +10118,7 @@
       <c r="N59" s="15"/>
       <c r="O59" s="22"/>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="19" t="s">
         <v>191</v>
       </c>
@@ -10157,7 +10161,7 @@
       <c r="N60" s="13"/>
       <c r="O60" s="20"/>
     </row>
-    <row r="61" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="21" t="s">
         <v>192</v>
       </c>
@@ -10200,7 +10204,7 @@
       <c r="N61" s="15"/>
       <c r="O61" s="22"/>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="19" t="s">
         <v>194</v>
       </c>
@@ -10243,7 +10247,7 @@
       <c r="N62" s="13"/>
       <c r="O62" s="20"/>
     </row>
-    <row r="63" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="21" t="s">
         <v>195</v>
       </c>
@@ -10286,7 +10290,7 @@
       <c r="N63" s="15"/>
       <c r="O63" s="22"/>
     </row>
-    <row r="64" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="19" t="s">
         <v>199</v>
       </c>
@@ -10329,7 +10333,7 @@
       <c r="N64" s="13"/>
       <c r="O64" s="20"/>
     </row>
-    <row r="65" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="21" t="s">
         <v>204</v>
       </c>
@@ -10372,7 +10376,7 @@
       <c r="N65" s="15"/>
       <c r="O65" s="22"/>
     </row>
-    <row r="66" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="19" t="s">
         <v>205</v>
       </c>
@@ -10415,7 +10419,7 @@
       <c r="N66" s="13"/>
       <c r="O66" s="20"/>
     </row>
-    <row r="67" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="21" t="s">
         <v>210</v>
       </c>
@@ -10458,7 +10462,7 @@
       <c r="N67" s="15"/>
       <c r="O67" s="22"/>
     </row>
-    <row r="68" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="19" t="s">
         <v>213</v>
       </c>
@@ -10503,7 +10507,7 @@
       </c>
       <c r="O68" s="20"/>
     </row>
-    <row r="69" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="21" t="s">
         <v>215</v>
       </c>
@@ -10546,7 +10550,7 @@
       <c r="N69" s="15"/>
       <c r="O69" s="22"/>
     </row>
-    <row r="70" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="19" t="s">
         <v>218</v>
       </c>
@@ -10589,7 +10593,7 @@
       <c r="N70" s="13"/>
       <c r="O70" s="20"/>
     </row>
-    <row r="71" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="21" t="s">
         <v>219</v>
       </c>
@@ -10632,7 +10636,7 @@
       <c r="N71" s="15"/>
       <c r="O71" s="22"/>
     </row>
-    <row r="72" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="19" t="s">
         <v>220</v>
       </c>
@@ -10675,7 +10679,7 @@
       <c r="N72" s="13"/>
       <c r="O72" s="20"/>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="21" t="s">
         <v>224</v>
       </c>
@@ -10718,7 +10722,7 @@
       <c r="N73" s="15"/>
       <c r="O73" s="22"/>
     </row>
-    <row r="74" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="19" t="s">
         <v>228</v>
       </c>
@@ -10761,7 +10765,7 @@
       <c r="N74" s="13"/>
       <c r="O74" s="20"/>
     </row>
-    <row r="75" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="21" t="s">
         <v>232</v>
       </c>
@@ -10804,7 +10808,7 @@
       <c r="N75" s="15"/>
       <c r="O75" s="22"/>
     </row>
-    <row r="76" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="19" t="s">
         <v>234</v>
       </c>
@@ -10847,7 +10851,7 @@
       <c r="N76" s="13"/>
       <c r="O76" s="20"/>
     </row>
-    <row r="77" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="21" t="s">
         <v>235</v>
       </c>
@@ -10890,7 +10894,7 @@
       <c r="N77" s="15"/>
       <c r="O77" s="22"/>
     </row>
-    <row r="78" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="19" t="s">
         <v>246</v>
       </c>
@@ -10933,7 +10937,7 @@
       <c r="N78" s="13"/>
       <c r="O78" s="20"/>
     </row>
-    <row r="79" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="21" t="s">
         <v>248</v>
       </c>
@@ -10976,7 +10980,7 @@
       <c r="N79" s="15"/>
       <c r="O79" s="22"/>
     </row>
-    <row r="80" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="19" t="s">
         <v>252</v>
       </c>
@@ -11021,7 +11025,7 @@
       </c>
       <c r="O80" s="20"/>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="21" t="s">
         <v>254</v>
       </c>
@@ -11064,7 +11068,7 @@
       <c r="N81" s="15"/>
       <c r="O81" s="22"/>
     </row>
-    <row r="82" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="19" t="s">
         <v>258</v>
       </c>
@@ -11109,7 +11113,7 @@
       </c>
       <c r="O82" s="20"/>
     </row>
-    <row r="83" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="21" t="s">
         <v>264</v>
       </c>
@@ -11152,7 +11156,7 @@
       <c r="N83" s="15"/>
       <c r="O83" s="22"/>
     </row>
-    <row r="84" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="19" t="s">
         <v>265</v>
       </c>
@@ -11195,7 +11199,7 @@
       <c r="N84" s="13"/>
       <c r="O84" s="20"/>
     </row>
-    <row r="85" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="21" t="s">
         <v>268</v>
       </c>
@@ -11240,7 +11244,7 @@
       </c>
       <c r="O85" s="22"/>
     </row>
-    <row r="86" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="19" t="s">
         <v>269</v>
       </c>
@@ -11283,7 +11287,7 @@
       <c r="N86" s="13"/>
       <c r="O86" s="20"/>
     </row>
-    <row r="87" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="21" t="s">
         <v>273</v>
       </c>
@@ -11326,7 +11330,7 @@
       <c r="N87" s="15"/>
       <c r="O87" s="22"/>
     </row>
-    <row r="88" spans="1:15" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="19" t="s">
         <v>275</v>
       </c>
@@ -11371,7 +11375,7 @@
       </c>
       <c r="O88" s="20"/>
     </row>
-    <row r="89" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="21" t="s">
         <v>276</v>
       </c>
@@ -11414,7 +11418,7 @@
       <c r="N89" s="15"/>
       <c r="O89" s="22"/>
     </row>
-    <row r="90" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="19" t="s">
         <v>278</v>
       </c>
@@ -11457,7 +11461,7 @@
       <c r="N90" s="13"/>
       <c r="O90" s="20"/>
     </row>
-    <row r="91" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="21" t="s">
         <v>285</v>
       </c>
@@ -11500,7 +11504,7 @@
       <c r="N91" s="15"/>
       <c r="O91" s="22"/>
     </row>
-    <row r="92" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="19" t="s">
         <v>287</v>
       </c>
@@ -11543,7 +11547,7 @@
       <c r="N92" s="13"/>
       <c r="O92" s="20"/>
     </row>
-    <row r="93" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="21" t="s">
         <v>292</v>
       </c>
@@ -11586,7 +11590,7 @@
       <c r="N93" s="15"/>
       <c r="O93" s="22"/>
     </row>
-    <row r="94" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="19" t="s">
         <v>293</v>
       </c>
@@ -11629,7 +11633,7 @@
       <c r="N94" s="13"/>
       <c r="O94" s="20"/>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="21" t="s">
         <v>296</v>
       </c>
@@ -11672,7 +11676,7 @@
       <c r="N95" s="15"/>
       <c r="O95" s="22"/>
     </row>
-    <row r="96" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="19" t="s">
         <v>298</v>
       </c>
@@ -11715,7 +11719,7 @@
       <c r="N96" s="13"/>
       <c r="O96" s="20"/>
     </row>
-    <row r="97" spans="1:15" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="21" t="s">
         <v>301</v>
       </c>
@@ -11758,7 +11762,7 @@
       <c r="N97" s="15"/>
       <c r="O97" s="22"/>
     </row>
-    <row r="98" spans="1:15" ht="144" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="19" t="s">
         <v>302</v>
       </c>
@@ -11801,7 +11805,7 @@
       <c r="N98" s="13"/>
       <c r="O98" s="20"/>
     </row>
-    <row r="99" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="21" t="s">
         <v>303</v>
       </c>
@@ -11844,7 +11848,7 @@
       <c r="N99" s="15"/>
       <c r="O99" s="22"/>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="19" t="s">
         <v>306</v>
       </c>
@@ -11887,7 +11891,7 @@
       <c r="N100" s="13"/>
       <c r="O100" s="20"/>
     </row>
-    <row r="101" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="21" t="s">
         <v>311</v>
       </c>
@@ -11932,7 +11936,7 @@
       </c>
       <c r="O101" s="22"/>
     </row>
-    <row r="102" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="19" t="s">
         <v>321</v>
       </c>
@@ -11975,7 +11979,7 @@
       <c r="N102" s="13"/>
       <c r="O102" s="20"/>
     </row>
-    <row r="103" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="21" t="s">
         <v>322</v>
       </c>
@@ -12020,7 +12024,7 @@
       </c>
       <c r="O103" s="22"/>
     </row>
-    <row r="104" spans="1:15" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="19" t="s">
         <v>323</v>
       </c>
@@ -12065,7 +12069,7 @@
       </c>
       <c r="O104" s="20"/>
     </row>
-    <row r="105" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="21" t="s">
         <v>325</v>
       </c>
@@ -12108,7 +12112,7 @@
       <c r="N105" s="15"/>
       <c r="O105" s="22"/>
     </row>
-    <row r="106" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="19" t="s">
         <v>327</v>
       </c>
@@ -12153,7 +12157,7 @@
       </c>
       <c r="O106" s="20"/>
     </row>
-    <row r="107" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="21" t="s">
         <v>328</v>
       </c>
@@ -12196,7 +12200,7 @@
       <c r="N107" s="15"/>
       <c r="O107" s="22"/>
     </row>
-    <row r="108" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="19" t="s">
         <v>333</v>
       </c>
@@ -12239,7 +12243,7 @@
       <c r="N108" s="13"/>
       <c r="O108" s="20"/>
     </row>
-    <row r="109" spans="1:15" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:15" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="21" t="s">
         <v>335</v>
       </c>
@@ -12282,7 +12286,7 @@
       <c r="N109" s="15"/>
       <c r="O109" s="22"/>
     </row>
-    <row r="110" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="19" t="s">
         <v>339</v>
       </c>
@@ -12325,7 +12329,7 @@
       <c r="N110" s="13"/>
       <c r="O110" s="20"/>
     </row>
-    <row r="111" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="21" t="s">
         <v>341</v>
       </c>
@@ -12368,7 +12372,7 @@
       <c r="N111" s="15"/>
       <c r="O111" s="22"/>
     </row>
-    <row r="112" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="19" t="s">
         <v>344</v>
       </c>
@@ -12411,7 +12415,7 @@
       <c r="N112" s="13"/>
       <c r="O112" s="20"/>
     </row>
-    <row r="113" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="21" t="s">
         <v>348</v>
       </c>
@@ -12454,7 +12458,7 @@
       <c r="N113" s="15"/>
       <c r="O113" s="22"/>
     </row>
-    <row r="114" spans="1:15" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:15" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="19" t="s">
         <v>350</v>
       </c>
@@ -12497,7 +12501,7 @@
       <c r="N114" s="13"/>
       <c r="O114" s="20"/>
     </row>
-    <row r="115" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="21" t="s">
         <v>358</v>
       </c>
@@ -12540,7 +12544,7 @@
       <c r="N115" s="15"/>
       <c r="O115" s="22"/>
     </row>
-    <row r="116" spans="1:15" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:15" ht="201.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="19" t="s">
         <v>360</v>
       </c>
@@ -12585,7 +12589,7 @@
       </c>
       <c r="O116" s="20"/>
     </row>
-    <row r="117" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="21" t="s">
         <v>362</v>
       </c>
@@ -12628,7 +12632,7 @@
       <c r="N117" s="15"/>
       <c r="O117" s="22"/>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="19" t="s">
         <v>374</v>
       </c>
@@ -12671,7 +12675,7 @@
       <c r="N118" s="13"/>
       <c r="O118" s="20"/>
     </row>
-    <row r="119" spans="1:15" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:15" ht="302.39999999999998" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="21" t="s">
         <v>380</v>
       </c>
@@ -12714,7 +12718,7 @@
       <c r="N119" s="15"/>
       <c r="O119" s="22"/>
     </row>
-    <row r="120" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="19" t="s">
         <v>383</v>
       </c>
@@ -12759,7 +12763,7 @@
       </c>
       <c r="O120" s="20"/>
     </row>
-    <row r="121" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="21" t="s">
         <v>389</v>
       </c>
@@ -12802,7 +12806,7 @@
       <c r="N121" s="15"/>
       <c r="O121" s="22"/>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="19" t="s">
         <v>392</v>
       </c>
@@ -12847,7 +12851,7 @@
       </c>
       <c r="O122" s="20"/>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="21" t="s">
         <v>395</v>
       </c>
@@ -12890,7 +12894,7 @@
       <c r="N123" s="15"/>
       <c r="O123" s="22"/>
     </row>
-    <row r="124" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="19" t="s">
         <v>398</v>
       </c>
@@ -12933,7 +12937,7 @@
       <c r="N124" s="13"/>
       <c r="O124" s="20"/>
     </row>
-    <row r="125" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="21" t="s">
         <v>400</v>
       </c>
@@ -12976,7 +12980,7 @@
       <c r="N125" s="15"/>
       <c r="O125" s="22"/>
     </row>
-    <row r="126" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="19" t="s">
         <v>401</v>
       </c>
@@ -13021,7 +13025,7 @@
       </c>
       <c r="O126" s="20"/>
     </row>
-    <row r="127" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="21" t="s">
         <v>404</v>
       </c>
@@ -13066,7 +13070,7 @@
       </c>
       <c r="O127" s="22"/>
     </row>
-    <row r="128" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="19" t="s">
         <v>407</v>
       </c>
@@ -13109,7 +13113,7 @@
       <c r="N128" s="13"/>
       <c r="O128" s="20"/>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="21" t="s">
         <v>411</v>
       </c>
@@ -13152,7 +13156,7 @@
       <c r="N129" s="15"/>
       <c r="O129" s="22"/>
     </row>
-    <row r="130" spans="1:15" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:15" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="19" t="s">
         <v>413</v>
       </c>
@@ -13195,7 +13199,7 @@
       <c r="N130" s="13"/>
       <c r="O130" s="20"/>
     </row>
-    <row r="131" spans="1:15" ht="273.60000000000002" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:15" ht="273.60000000000002" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="21" t="s">
         <v>415</v>
       </c>
@@ -13240,7 +13244,7 @@
       </c>
       <c r="O131" s="22"/>
     </row>
-    <row r="132" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="19" t="s">
         <v>417</v>
       </c>
@@ -13283,7 +13287,7 @@
       <c r="N132" s="13"/>
       <c r="O132" s="20"/>
     </row>
-    <row r="133" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="21" t="s">
         <v>419</v>
       </c>
@@ -13328,7 +13332,7 @@
       </c>
       <c r="O133" s="22"/>
     </row>
-    <row r="134" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="19" t="s">
         <v>425</v>
       </c>
@@ -13371,7 +13375,7 @@
       <c r="N134" s="13"/>
       <c r="O134" s="20"/>
     </row>
-    <row r="135" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="21" t="s">
         <v>426</v>
       </c>
@@ -13416,7 +13420,7 @@
       </c>
       <c r="O135" s="22"/>
     </row>
-    <row r="136" spans="1:15" ht="345.6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:15" ht="345.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="19" t="s">
         <v>427</v>
       </c>
@@ -13461,7 +13465,7 @@
       </c>
       <c r="O136" s="20"/>
     </row>
-    <row r="137" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="21" t="s">
         <v>429</v>
       </c>
@@ -13506,7 +13510,7 @@
       </c>
       <c r="O137" s="22"/>
     </row>
-    <row r="138" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="19" t="s">
         <v>430</v>
       </c>
@@ -13549,7 +13553,7 @@
       <c r="N138" s="13"/>
       <c r="O138" s="20"/>
     </row>
-    <row r="139" spans="1:15" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:15" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="21" t="s">
         <v>431</v>
       </c>
@@ -13592,7 +13596,7 @@
       <c r="N139" s="15"/>
       <c r="O139" s="22"/>
     </row>
-    <row r="140" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="19" t="s">
         <v>433</v>
       </c>
@@ -13637,7 +13641,7 @@
       </c>
       <c r="O140" s="20"/>
     </row>
-    <row r="141" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="21" t="s">
         <v>434</v>
       </c>
@@ -13680,7 +13684,7 @@
       <c r="N141" s="15"/>
       <c r="O141" s="22"/>
     </row>
-    <row r="142" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="19" t="s">
         <v>439</v>
       </c>
@@ -13723,7 +13727,7 @@
       <c r="N142" s="13"/>
       <c r="O142" s="20"/>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="21" t="s">
         <v>442</v>
       </c>
@@ -13766,7 +13770,7 @@
       <c r="N143" s="15"/>
       <c r="O143" s="22"/>
     </row>
-    <row r="144" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="19" t="s">
         <v>446</v>
       </c>
@@ -13809,7 +13813,7 @@
       <c r="N144" s="13"/>
       <c r="O144" s="20"/>
     </row>
-    <row r="145" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="21" t="s">
         <v>447</v>
       </c>
@@ -13852,7 +13856,7 @@
       <c r="N145" s="15"/>
       <c r="O145" s="22"/>
     </row>
-    <row r="146" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="19" t="s">
         <v>448</v>
       </c>
@@ -13897,7 +13901,7 @@
       </c>
       <c r="O146" s="20"/>
     </row>
-    <row r="147" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="21" t="s">
         <v>449</v>
       </c>
@@ -13940,7 +13944,7 @@
       <c r="N147" s="15"/>
       <c r="O147" s="22"/>
     </row>
-    <row r="148" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="19" t="s">
         <v>452</v>
       </c>
@@ -13983,7 +13987,7 @@
       <c r="N148" s="13"/>
       <c r="O148" s="20"/>
     </row>
-    <row r="149" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="21" t="s">
         <v>453</v>
       </c>
@@ -14026,7 +14030,7 @@
       <c r="N149" s="15"/>
       <c r="O149" s="22"/>
     </row>
-    <row r="150" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="19" t="s">
         <v>456</v>
       </c>
@@ -14069,7 +14073,7 @@
       <c r="N150" s="13"/>
       <c r="O150" s="20"/>
     </row>
-    <row r="151" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="21" t="s">
         <v>459</v>
       </c>
@@ -14112,7 +14116,7 @@
       <c r="N151" s="15"/>
       <c r="O151" s="22"/>
     </row>
-    <row r="152" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="19" t="s">
         <v>463</v>
       </c>
@@ -14155,7 +14159,7 @@
       <c r="N152" s="13"/>
       <c r="O152" s="20"/>
     </row>
-    <row r="153" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="21" t="s">
         <v>468</v>
       </c>
@@ -14198,7 +14202,7 @@
       <c r="N153" s="15"/>
       <c r="O153" s="22"/>
     </row>
-    <row r="154" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="19" t="s">
         <v>471</v>
       </c>
@@ -14241,7 +14245,7 @@
       <c r="N154" s="13"/>
       <c r="O154" s="20"/>
     </row>
-    <row r="155" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="21" t="s">
         <v>475</v>
       </c>
@@ -14284,7 +14288,7 @@
       <c r="N155" s="15"/>
       <c r="O155" s="22"/>
     </row>
-    <row r="156" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="19" t="s">
         <v>478</v>
       </c>
@@ -14327,7 +14331,7 @@
       <c r="N156" s="13"/>
       <c r="O156" s="20"/>
     </row>
-    <row r="157" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="21" t="s">
         <v>481</v>
       </c>
@@ -14370,7 +14374,7 @@
       <c r="N157" s="15"/>
       <c r="O157" s="22"/>
     </row>
-    <row r="158" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="19" t="s">
         <v>487</v>
       </c>
@@ -14413,7 +14417,7 @@
       <c r="N158" s="13"/>
       <c r="O158" s="20"/>
     </row>
-    <row r="159" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="21" t="s">
         <v>491</v>
       </c>
@@ -14456,7 +14460,7 @@
       <c r="N159" s="15"/>
       <c r="O159" s="22"/>
     </row>
-    <row r="160" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="19" t="s">
         <v>493</v>
       </c>
@@ -14499,7 +14503,7 @@
       <c r="N160" s="13"/>
       <c r="O160" s="20"/>
     </row>
-    <row r="161" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="21" t="s">
         <v>494</v>
       </c>
@@ -14544,7 +14548,7 @@
       </c>
       <c r="O161" s="22"/>
     </row>
-    <row r="162" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="19" t="s">
         <v>495</v>
       </c>
@@ -14587,7 +14591,7 @@
       <c r="N162" s="13"/>
       <c r="O162" s="20"/>
     </row>
-    <row r="163" spans="1:15" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:15" ht="201.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="21" t="s">
         <v>498</v>
       </c>
@@ -14630,7 +14634,7 @@
       <c r="N163" s="15"/>
       <c r="O163" s="22"/>
     </row>
-    <row r="164" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="19" t="s">
         <v>503</v>
       </c>
@@ -14673,7 +14677,7 @@
       <c r="N164" s="13"/>
       <c r="O164" s="20"/>
     </row>
-    <row r="165" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="21" t="s">
         <v>504</v>
       </c>
@@ -14716,7 +14720,7 @@
       <c r="N165" s="15"/>
       <c r="O165" s="22"/>
     </row>
-    <row r="166" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="19" t="s">
         <v>508</v>
       </c>
@@ -14759,7 +14763,7 @@
       <c r="N166" s="13"/>
       <c r="O166" s="20"/>
     </row>
-    <row r="167" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="21" t="s">
         <v>510</v>
       </c>
@@ -14802,7 +14806,7 @@
       <c r="N167" s="15"/>
       <c r="O167" s="22"/>
     </row>
-    <row r="168" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="19" t="s">
         <v>512</v>
       </c>
@@ -14847,7 +14851,7 @@
       </c>
       <c r="O168" s="20"/>
     </row>
-    <row r="169" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="21" t="s">
         <v>516</v>
       </c>
@@ -14890,7 +14894,7 @@
       <c r="N169" s="15"/>
       <c r="O169" s="22"/>
     </row>
-    <row r="170" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="19" t="s">
         <v>518</v>
       </c>
@@ -14933,7 +14937,7 @@
       <c r="N170" s="13"/>
       <c r="O170" s="20"/>
     </row>
-    <row r="171" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="21" t="s">
         <v>523</v>
       </c>
@@ -14976,7 +14980,7 @@
       <c r="N171" s="15"/>
       <c r="O171" s="22"/>
     </row>
-    <row r="172" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="19" t="s">
         <v>525</v>
       </c>
@@ -15019,7 +15023,7 @@
       <c r="N172" s="13"/>
       <c r="O172" s="20"/>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="21" t="s">
         <v>531</v>
       </c>
@@ -15062,7 +15066,7 @@
       <c r="N173" s="15"/>
       <c r="O173" s="22"/>
     </row>
-    <row r="174" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="19" t="s">
         <v>539</v>
       </c>
@@ -15105,7 +15109,7 @@
       <c r="N174" s="13"/>
       <c r="O174" s="20"/>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="21" t="s">
         <v>541</v>
       </c>
@@ -15150,7 +15154,7 @@
       </c>
       <c r="O175" s="22"/>
     </row>
-    <row r="176" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="19" t="s">
         <v>542</v>
       </c>
@@ -15193,7 +15197,7 @@
       <c r="N176" s="13"/>
       <c r="O176" s="20"/>
     </row>
-    <row r="177" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="21" t="s">
         <v>544</v>
       </c>
@@ -15236,7 +15240,7 @@
       <c r="N177" s="15"/>
       <c r="O177" s="22"/>
     </row>
-    <row r="178" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="19" t="s">
         <v>545</v>
       </c>
@@ -15279,7 +15283,7 @@
       <c r="N178" s="13"/>
       <c r="O178" s="20"/>
     </row>
-    <row r="179" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="21" t="s">
         <v>546</v>
       </c>
@@ -15322,7 +15326,7 @@
       <c r="N179" s="15"/>
       <c r="O179" s="22"/>
     </row>
-    <row r="180" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="19" t="s">
         <v>548</v>
       </c>
@@ -15367,7 +15371,7 @@
       </c>
       <c r="O180" s="20"/>
     </row>
-    <row r="181" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="21" t="s">
         <v>550</v>
       </c>
@@ -15410,7 +15414,7 @@
       <c r="N181" s="15"/>
       <c r="O181" s="22"/>
     </row>
-    <row r="182" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="19" t="s">
         <v>552</v>
       </c>
@@ -15455,7 +15459,7 @@
       </c>
       <c r="O182" s="20"/>
     </row>
-    <row r="183" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="21" t="s">
         <v>556</v>
       </c>
@@ -15500,7 +15504,7 @@
       </c>
       <c r="O183" s="22"/>
     </row>
-    <row r="184" spans="1:15" ht="216" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:15" ht="216" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="19" t="s">
         <v>560</v>
       </c>
@@ -15543,7 +15547,7 @@
       <c r="N184" s="13"/>
       <c r="O184" s="20"/>
     </row>
-    <row r="185" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="21" t="s">
         <v>561</v>
       </c>
@@ -15586,7 +15590,7 @@
       <c r="N185" s="15"/>
       <c r="O185" s="22"/>
     </row>
-    <row r="186" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="19" t="s">
         <v>562</v>
       </c>
@@ -15629,7 +15633,7 @@
       <c r="N186" s="13"/>
       <c r="O186" s="20"/>
     </row>
-    <row r="187" spans="1:15" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:15" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="21" t="s">
         <v>564</v>
       </c>
@@ -15672,7 +15676,7 @@
       <c r="N187" s="15"/>
       <c r="O187" s="22"/>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="19" t="s">
         <v>565</v>
       </c>
@@ -15715,7 +15719,7 @@
       <c r="N188" s="13"/>
       <c r="O188" s="20"/>
     </row>
-    <row r="189" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="21" t="s">
         <v>566</v>
       </c>
@@ -15758,7 +15762,7 @@
       <c r="N189" s="15"/>
       <c r="O189" s="22"/>
     </row>
-    <row r="190" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="19" t="s">
         <v>570</v>
       </c>
@@ -15801,7 +15805,7 @@
       <c r="N190" s="13"/>
       <c r="O190" s="20"/>
     </row>
-    <row r="191" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="21" t="s">
         <v>571</v>
       </c>
@@ -15846,7 +15850,7 @@
       </c>
       <c r="O191" s="22"/>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="19" t="s">
         <v>573</v>
       </c>
@@ -15889,7 +15893,7 @@
       <c r="N192" s="13"/>
       <c r="O192" s="20"/>
     </row>
-    <row r="193" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="21" t="s">
         <v>575</v>
       </c>
@@ -15932,7 +15936,7 @@
       <c r="N193" s="15"/>
       <c r="O193" s="22"/>
     </row>
-    <row r="194" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="19" t="s">
         <v>580</v>
       </c>
@@ -15975,7 +15979,7 @@
       <c r="N194" s="13"/>
       <c r="O194" s="20"/>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="21" t="s">
         <v>582</v>
       </c>
@@ -16018,7 +16022,7 @@
       <c r="N195" s="15"/>
       <c r="O195" s="22"/>
     </row>
-    <row r="196" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="19" t="s">
         <v>583</v>
       </c>
@@ -16063,7 +16067,7 @@
       </c>
       <c r="O196" s="20"/>
     </row>
-    <row r="197" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="21" t="s">
         <v>585</v>
       </c>
@@ -16108,7 +16112,7 @@
       </c>
       <c r="O197" s="22"/>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="19" t="s">
         <v>590</v>
       </c>
@@ -16151,7 +16155,7 @@
       <c r="N198" s="13"/>
       <c r="O198" s="20"/>
     </row>
-    <row r="199" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="21" t="s">
         <v>592</v>
       </c>
@@ -16196,7 +16200,7 @@
       </c>
       <c r="O199" s="22"/>
     </row>
-    <row r="200" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="19" t="s">
         <v>597</v>
       </c>
@@ -16239,7 +16243,7 @@
       <c r="N200" s="13"/>
       <c r="O200" s="20"/>
     </row>
-    <row r="201" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="21" t="s">
         <v>598</v>
       </c>
@@ -16282,7 +16286,7 @@
       <c r="N201" s="15"/>
       <c r="O201" s="22"/>
     </row>
-    <row r="202" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="19" t="s">
         <v>602</v>
       </c>
@@ -16325,7 +16329,7 @@
       <c r="N202" s="13"/>
       <c r="O202" s="20"/>
     </row>
-    <row r="203" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="21" t="s">
         <v>604</v>
       </c>
@@ -16368,7 +16372,7 @@
       <c r="N203" s="15"/>
       <c r="O203" s="22"/>
     </row>
-    <row r="204" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="19" t="s">
         <v>607</v>
       </c>
@@ -16411,7 +16415,7 @@
       <c r="N204" s="13"/>
       <c r="O204" s="20"/>
     </row>
-    <row r="205" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="21" t="s">
         <v>614</v>
       </c>
@@ -16454,7 +16458,7 @@
       <c r="N205" s="15"/>
       <c r="O205" s="22"/>
     </row>
-    <row r="206" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="19" t="s">
         <v>616</v>
       </c>
@@ -16497,7 +16501,7 @@
       <c r="N206" s="13"/>
       <c r="O206" s="20"/>
     </row>
-    <row r="207" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="21" t="s">
         <v>619</v>
       </c>
@@ -16540,7 +16544,7 @@
       <c r="N207" s="15"/>
       <c r="O207" s="22"/>
     </row>
-    <row r="208" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="19" t="s">
         <v>626</v>
       </c>
@@ -16583,7 +16587,7 @@
       <c r="N208" s="13"/>
       <c r="O208" s="20"/>
     </row>
-    <row r="209" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="21" t="s">
         <v>629</v>
       </c>
@@ -16626,7 +16630,7 @@
       <c r="N209" s="15"/>
       <c r="O209" s="22"/>
     </row>
-    <row r="210" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="19" t="s">
         <v>631</v>
       </c>
@@ -16669,7 +16673,7 @@
       <c r="N210" s="13"/>
       <c r="O210" s="20"/>
     </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="21" t="s">
         <v>642</v>
       </c>
@@ -16712,7 +16716,7 @@
       <c r="N211" s="15"/>
       <c r="O211" s="22"/>
     </row>
-    <row r="212" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="19" t="s">
         <v>644</v>
       </c>
@@ -16755,7 +16759,7 @@
       <c r="N212" s="13"/>
       <c r="O212" s="20"/>
     </row>
-    <row r="213" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="21" t="s">
         <v>645</v>
       </c>
@@ -16800,7 +16804,7 @@
       </c>
       <c r="O213" s="22"/>
     </row>
-    <row r="214" spans="1:15" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:15" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="19" t="s">
         <v>648</v>
       </c>
@@ -16843,7 +16847,7 @@
       <c r="N214" s="13"/>
       <c r="O214" s="20"/>
     </row>
-    <row r="215" spans="1:15" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:15" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="21" t="s">
         <v>650</v>
       </c>
@@ -16886,7 +16890,7 @@
       <c r="N215" s="15"/>
       <c r="O215" s="22"/>
     </row>
-    <row r="216" spans="1:15" ht="288" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:15" ht="288" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="19" t="s">
         <v>655</v>
       </c>
@@ -16929,7 +16933,7 @@
       <c r="N216" s="13"/>
       <c r="O216" s="20"/>
     </row>
-    <row r="217" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="21" t="s">
         <v>658</v>
       </c>
@@ -16972,7 +16976,7 @@
       <c r="N217" s="15"/>
       <c r="O217" s="22"/>
     </row>
-    <row r="218" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="19" t="s">
         <v>660</v>
       </c>
@@ -17015,7 +17019,7 @@
       <c r="N218" s="13"/>
       <c r="O218" s="20"/>
     </row>
-    <row r="219" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="21" t="s">
         <v>661</v>
       </c>
@@ -17058,7 +17062,7 @@
       <c r="N219" s="15"/>
       <c r="O219" s="22"/>
     </row>
-    <row r="220" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="19" t="s">
         <v>665</v>
       </c>
@@ -17101,7 +17105,7 @@
       <c r="N220" s="13"/>
       <c r="O220" s="20"/>
     </row>
-    <row r="221" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="21" t="s">
         <v>667</v>
       </c>
@@ -17144,7 +17148,7 @@
       <c r="N221" s="15"/>
       <c r="O221" s="22"/>
     </row>
-    <row r="222" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="19" t="s">
         <v>668</v>
       </c>
@@ -17189,7 +17193,7 @@
       </c>
       <c r="O222" s="20"/>
     </row>
-    <row r="223" spans="1:15" ht="259.2" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:15" ht="259.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="21" t="s">
         <v>669</v>
       </c>
@@ -17234,7 +17238,7 @@
       </c>
       <c r="O223" s="22"/>
     </row>
-    <row r="224" spans="1:15" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:15" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="19" t="s">
         <v>670</v>
       </c>
@@ -17277,7 +17281,7 @@
       <c r="N224" s="13"/>
       <c r="O224" s="20"/>
     </row>
-    <row r="225" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="21" t="s">
         <v>672</v>
       </c>
@@ -17322,7 +17326,7 @@
       </c>
       <c r="O225" s="22"/>
     </row>
-    <row r="226" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="19" t="s">
         <v>674</v>
       </c>
@@ -17365,7 +17369,7 @@
       <c r="N226" s="13"/>
       <c r="O226" s="20"/>
     </row>
-    <row r="227" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="21" t="s">
         <v>676</v>
       </c>
@@ -17408,7 +17412,7 @@
       <c r="N227" s="15"/>
       <c r="O227" s="22"/>
     </row>
-    <row r="228" spans="1:15" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:15" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="19" t="s">
         <v>685</v>
       </c>
@@ -17453,7 +17457,7 @@
       </c>
       <c r="O228" s="20"/>
     </row>
-    <row r="229" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="21" t="s">
         <v>687</v>
       </c>
@@ -17496,7 +17500,7 @@
       <c r="N229" s="15"/>
       <c r="O229" s="22"/>
     </row>
-    <row r="230" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="19" t="s">
         <v>689</v>
       </c>
@@ -17541,7 +17545,7 @@
       </c>
       <c r="O230" s="20"/>
     </row>
-    <row r="231" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="21" t="s">
         <v>693</v>
       </c>
@@ -17584,7 +17588,7 @@
       <c r="N231" s="15"/>
       <c r="O231" s="22"/>
     </row>
-    <row r="232" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="19" t="s">
         <v>694</v>
       </c>
@@ -17627,7 +17631,7 @@
       <c r="N232" s="13"/>
       <c r="O232" s="20"/>
     </row>
-    <row r="233" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="21" t="s">
         <v>696</v>
       </c>
@@ -17670,7 +17674,7 @@
       <c r="N233" s="15"/>
       <c r="O233" s="22"/>
     </row>
-    <row r="234" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="19" t="s">
         <v>699</v>
       </c>
@@ -17713,7 +17717,7 @@
       <c r="N234" s="13"/>
       <c r="O234" s="20"/>
     </row>
-    <row r="235" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="21" t="s">
         <v>701</v>
       </c>
@@ -17756,7 +17760,7 @@
       <c r="N235" s="15"/>
       <c r="O235" s="22"/>
     </row>
-    <row r="236" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="19" t="s">
         <v>703</v>
       </c>
@@ -17799,7 +17803,7 @@
       <c r="N236" s="13"/>
       <c r="O236" s="20"/>
     </row>
-    <row r="237" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="21" t="s">
         <v>704</v>
       </c>
@@ -17842,7 +17846,7 @@
       <c r="N237" s="15"/>
       <c r="O237" s="22"/>
     </row>
-    <row r="238" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="19" t="s">
         <v>706</v>
       </c>
@@ -17885,7 +17889,7 @@
       <c r="N238" s="13"/>
       <c r="O238" s="20"/>
     </row>
-    <row r="239" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="21" t="s">
         <v>708</v>
       </c>
@@ -17928,7 +17932,7 @@
       <c r="N239" s="15"/>
       <c r="O239" s="22"/>
     </row>
-    <row r="240" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="19" t="s">
         <v>709</v>
       </c>
@@ -17973,7 +17977,7 @@
       </c>
       <c r="O240" s="20"/>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="21" t="s">
         <v>711</v>
       </c>
@@ -18016,7 +18020,7 @@
       <c r="N241" s="15"/>
       <c r="O241" s="22"/>
     </row>
-    <row r="242" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="19" t="s">
         <v>712</v>
       </c>
@@ -18059,7 +18063,7 @@
       <c r="N242" s="13"/>
       <c r="O242" s="20"/>
     </row>
-    <row r="243" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="21" t="s">
         <v>713</v>
       </c>
@@ -18104,7 +18108,7 @@
       </c>
       <c r="O243" s="22"/>
     </row>
-    <row r="244" spans="1:15" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:15" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="19" t="s">
         <v>716</v>
       </c>
@@ -18189,10 +18193,12 @@
       <c r="M245" s="15" t="s">
         <v>2300</v>
       </c>
-      <c r="N245" s="15"/>
+      <c r="N245" s="15" t="s">
+        <v>2301</v>
+      </c>
       <c r="O245" s="22"/>
     </row>
-    <row r="246" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="19" t="s">
         <v>724</v>
       </c>
@@ -18235,7 +18241,7 @@
       <c r="N246" s="13"/>
       <c r="O246" s="20"/>
     </row>
-    <row r="247" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="21" t="s">
         <v>726</v>
       </c>
@@ -18278,7 +18284,7 @@
       <c r="N247" s="15"/>
       <c r="O247" s="22"/>
     </row>
-    <row r="248" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="19" t="s">
         <v>728</v>
       </c>
@@ -18321,7 +18327,7 @@
       <c r="N248" s="13"/>
       <c r="O248" s="20"/>
     </row>
-    <row r="249" spans="1:15" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:15" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="21" t="s">
         <v>730</v>
       </c>
@@ -18364,7 +18370,7 @@
       <c r="N249" s="15"/>
       <c r="O249" s="22"/>
     </row>
-    <row r="250" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="19" t="s">
         <v>733</v>
       </c>
@@ -18409,7 +18415,7 @@
       </c>
       <c r="O250" s="20"/>
     </row>
-    <row r="251" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="21" t="s">
         <v>735</v>
       </c>
@@ -18452,7 +18458,7 @@
       <c r="N251" s="15"/>
       <c r="O251" s="22"/>
     </row>
-    <row r="252" spans="1:15" ht="144" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:15" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="19" t="s">
         <v>742</v>
       </c>
@@ -18495,7 +18501,7 @@
       <c r="N252" s="13"/>
       <c r="O252" s="20"/>
     </row>
-    <row r="253" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="21" t="s">
         <v>744</v>
       </c>
@@ -18538,7 +18544,7 @@
       <c r="N253" s="15"/>
       <c r="O253" s="22"/>
     </row>
-    <row r="254" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="19" t="s">
         <v>747</v>
       </c>
@@ -18581,7 +18587,7 @@
       <c r="N254" s="13"/>
       <c r="O254" s="20"/>
     </row>
-    <row r="255" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="21" t="s">
         <v>749</v>
       </c>
@@ -18624,7 +18630,7 @@
       <c r="N255" s="15"/>
       <c r="O255" s="22"/>
     </row>
-    <row r="256" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="19" t="s">
         <v>751</v>
       </c>
@@ -18667,7 +18673,7 @@
       <c r="N256" s="13"/>
       <c r="O256" s="20"/>
     </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="21" t="s">
         <v>758</v>
       </c>
@@ -18710,7 +18716,7 @@
       <c r="N257" s="15"/>
       <c r="O257" s="22"/>
     </row>
-    <row r="258" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="19" t="s">
         <v>760</v>
       </c>
@@ -18755,7 +18761,7 @@
       </c>
       <c r="O258" s="20"/>
     </row>
-    <row r="259" spans="1:15" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:15" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="21" t="s">
         <v>762</v>
       </c>
@@ -18798,7 +18804,7 @@
       <c r="N259" s="15"/>
       <c r="O259" s="22"/>
     </row>
-    <row r="260" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="19" t="s">
         <v>766</v>
       </c>
@@ -18841,7 +18847,7 @@
       <c r="N260" s="13"/>
       <c r="O260" s="20"/>
     </row>
-    <row r="261" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="21" t="s">
         <v>767</v>
       </c>
@@ -18884,7 +18890,7 @@
       <c r="N261" s="15"/>
       <c r="O261" s="22"/>
     </row>
-    <row r="262" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="19" t="s">
         <v>768</v>
       </c>
@@ -18927,7 +18933,7 @@
       <c r="N262" s="13"/>
       <c r="O262" s="20"/>
     </row>
-    <row r="263" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="21" t="s">
         <v>772</v>
       </c>
@@ -18970,7 +18976,7 @@
       <c r="N263" s="15"/>
       <c r="O263" s="22"/>
     </row>
-    <row r="264" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="19" t="s">
         <v>774</v>
       </c>
@@ -19013,7 +19019,7 @@
       <c r="N264" s="13"/>
       <c r="O264" s="20"/>
     </row>
-    <row r="265" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="21" t="s">
         <v>780</v>
       </c>
@@ -19056,7 +19062,7 @@
       <c r="N265" s="15"/>
       <c r="O265" s="22"/>
     </row>
-    <row r="266" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="19" t="s">
         <v>784</v>
       </c>
@@ -19101,7 +19107,7 @@
       </c>
       <c r="O266" s="20"/>
     </row>
-    <row r="267" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" s="21" t="s">
         <v>786</v>
       </c>
@@ -19146,7 +19152,7 @@
       </c>
       <c r="O267" s="22"/>
     </row>
-    <row r="268" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="19" t="s">
         <v>789</v>
       </c>
@@ -19189,7 +19195,7 @@
       <c r="N268" s="13"/>
       <c r="O268" s="20"/>
     </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="21" t="s">
         <v>790</v>
       </c>
@@ -19232,7 +19238,7 @@
       <c r="N269" s="15"/>
       <c r="O269" s="22"/>
     </row>
-    <row r="270" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="19" t="s">
         <v>792</v>
       </c>
@@ -19275,7 +19281,7 @@
       <c r="N270" s="13"/>
       <c r="O270" s="20"/>
     </row>
-    <row r="271" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="21" t="s">
         <v>793</v>
       </c>
@@ -19318,7 +19324,7 @@
       <c r="N271" s="15"/>
       <c r="O271" s="22"/>
     </row>
-    <row r="272" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="19" t="s">
         <v>795</v>
       </c>
@@ -19363,7 +19369,7 @@
       </c>
       <c r="O272" s="20"/>
     </row>
-    <row r="273" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="21" t="s">
         <v>802</v>
       </c>
@@ -19406,7 +19412,7 @@
       <c r="N273" s="15"/>
       <c r="O273" s="22"/>
     </row>
-    <row r="274" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="19" t="s">
         <v>804</v>
       </c>
@@ -19451,7 +19457,7 @@
       </c>
       <c r="O274" s="20"/>
     </row>
-    <row r="275" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" s="21" t="s">
         <v>812</v>
       </c>
@@ -19494,7 +19500,7 @@
       <c r="N275" s="15"/>
       <c r="O275" s="22"/>
     </row>
-    <row r="276" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="19" t="s">
         <v>816</v>
       </c>
@@ -19537,7 +19543,7 @@
       <c r="N276" s="13"/>
       <c r="O276" s="20"/>
     </row>
-    <row r="277" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" s="21" t="s">
         <v>818</v>
       </c>
@@ -19580,7 +19586,7 @@
       <c r="N277" s="15"/>
       <c r="O277" s="22"/>
     </row>
-    <row r="278" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" s="19" t="s">
         <v>822</v>
       </c>
@@ -19623,7 +19629,7 @@
       <c r="N278" s="13"/>
       <c r="O278" s="20"/>
     </row>
-    <row r="279" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="21" t="s">
         <v>828</v>
       </c>
@@ -19666,7 +19672,7 @@
       <c r="N279" s="15"/>
       <c r="O279" s="22"/>
     </row>
-    <row r="280" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="19" t="s">
         <v>830</v>
       </c>
@@ -19709,7 +19715,7 @@
       <c r="N280" s="13"/>
       <c r="O280" s="20"/>
     </row>
-    <row r="281" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" s="21" t="s">
         <v>834</v>
       </c>
@@ -19752,7 +19758,7 @@
       <c r="N281" s="15"/>
       <c r="O281" s="22"/>
     </row>
-    <row r="282" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" s="19" t="s">
         <v>835</v>
       </c>
@@ -19795,7 +19801,7 @@
       <c r="N282" s="13"/>
       <c r="O282" s="20"/>
     </row>
-    <row r="283" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" s="21" t="s">
         <v>839</v>
       </c>
@@ -19838,7 +19844,7 @@
       <c r="N283" s="15"/>
       <c r="O283" s="22"/>
     </row>
-    <row r="284" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" s="19" t="s">
         <v>840</v>
       </c>
@@ -19881,7 +19887,7 @@
       <c r="N284" s="13"/>
       <c r="O284" s="20"/>
     </row>
-    <row r="285" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" s="21" t="s">
         <v>842</v>
       </c>
@@ -19924,7 +19930,7 @@
       <c r="N285" s="15"/>
       <c r="O285" s="22"/>
     </row>
-    <row r="286" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" s="19" t="s">
         <v>843</v>
       </c>
@@ -19967,7 +19973,7 @@
       <c r="N286" s="13"/>
       <c r="O286" s="20"/>
     </row>
-    <row r="287" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" s="21" t="s">
         <v>847</v>
       </c>
@@ -20012,7 +20018,7 @@
       </c>
       <c r="O287" s="22"/>
     </row>
-    <row r="288" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" s="19" t="s">
         <v>848</v>
       </c>
@@ -20055,7 +20061,7 @@
       <c r="N288" s="13"/>
       <c r="O288" s="20"/>
     </row>
-    <row r="289" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" s="21" t="s">
         <v>850</v>
       </c>
@@ -20098,7 +20104,7 @@
       <c r="N289" s="15"/>
       <c r="O289" s="22"/>
     </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" s="19" t="s">
         <v>853</v>
       </c>
@@ -20141,7 +20147,7 @@
       <c r="N290" s="13"/>
       <c r="O290" s="20"/>
     </row>
-    <row r="291" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" s="21" t="s">
         <v>857</v>
       </c>
@@ -20186,7 +20192,7 @@
       </c>
       <c r="O291" s="22"/>
     </row>
-    <row r="292" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" s="19" t="s">
         <v>860</v>
       </c>
@@ -20231,7 +20237,7 @@
       </c>
       <c r="O292" s="20"/>
     </row>
-    <row r="293" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" s="21" t="s">
         <v>862</v>
       </c>
@@ -20274,7 +20280,7 @@
       <c r="N293" s="15"/>
       <c r="O293" s="22"/>
     </row>
-    <row r="294" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="19" t="s">
         <v>864</v>
       </c>
@@ -20319,7 +20325,7 @@
       </c>
       <c r="O294" s="20"/>
     </row>
-    <row r="295" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="21" t="s">
         <v>880</v>
       </c>
@@ -20362,7 +20368,7 @@
       <c r="N295" s="15"/>
       <c r="O295" s="22"/>
     </row>
-    <row r="296" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="19" t="s">
         <v>883</v>
       </c>
@@ -20407,7 +20413,7 @@
       </c>
       <c r="O296" s="20"/>
     </row>
-    <row r="297" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="21" t="s">
         <v>888</v>
       </c>
@@ -20450,7 +20456,7 @@
       <c r="N297" s="15"/>
       <c r="O297" s="22"/>
     </row>
-    <row r="298" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="19" t="s">
         <v>890</v>
       </c>
@@ -20495,7 +20501,7 @@
       </c>
       <c r="O298" s="20"/>
     </row>
-    <row r="299" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="21" t="s">
         <v>899</v>
       </c>
@@ -20538,7 +20544,7 @@
       <c r="N299" s="15"/>
       <c r="O299" s="22"/>
     </row>
-    <row r="300" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="19" t="s">
         <v>902</v>
       </c>
@@ -20581,7 +20587,7 @@
       <c r="N300" s="13"/>
       <c r="O300" s="20"/>
     </row>
-    <row r="301" spans="1:15" ht="144" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:15" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="21" t="s">
         <v>904</v>
       </c>
@@ -20626,7 +20632,7 @@
       </c>
       <c r="O301" s="22"/>
     </row>
-    <row r="302" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" s="19" t="s">
         <v>914</v>
       </c>
@@ -20669,7 +20675,7 @@
       <c r="N302" s="13"/>
       <c r="O302" s="20"/>
     </row>
-    <row r="303" spans="1:15" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:15" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="21" t="s">
         <v>916</v>
       </c>
@@ -20714,7 +20720,7 @@
       </c>
       <c r="O303" s="22"/>
     </row>
-    <row r="304" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="19" t="s">
         <v>917</v>
       </c>
@@ -20757,7 +20763,7 @@
       <c r="N304" s="13"/>
       <c r="O304" s="20"/>
     </row>
-    <row r="305" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="21" t="s">
         <v>919</v>
       </c>
@@ -20800,7 +20806,7 @@
       <c r="N305" s="15"/>
       <c r="O305" s="22"/>
     </row>
-    <row r="306" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" s="19" t="s">
         <v>922</v>
       </c>
@@ -20843,7 +20849,7 @@
       <c r="N306" s="13"/>
       <c r="O306" s="20"/>
     </row>
-    <row r="307" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" s="21" t="s">
         <v>925</v>
       </c>
@@ -20886,7 +20892,7 @@
       <c r="N307" s="15"/>
       <c r="O307" s="22"/>
     </row>
-    <row r="308" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="19" t="s">
         <v>927</v>
       </c>
@@ -20929,7 +20935,7 @@
       <c r="N308" s="13"/>
       <c r="O308" s="20"/>
     </row>
-    <row r="309" spans="1:15" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:15" ht="302.39999999999998" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="21" t="s">
         <v>929</v>
       </c>
@@ -20972,7 +20978,7 @@
       <c r="N309" s="15"/>
       <c r="O309" s="22"/>
     </row>
-    <row r="310" spans="1:15" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:15" ht="187.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" s="19" t="s">
         <v>931</v>
       </c>
@@ -21015,7 +21021,7 @@
       <c r="N310" s="13"/>
       <c r="O310" s="20"/>
     </row>
-    <row r="311" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" s="21" t="s">
         <v>933</v>
       </c>
@@ -21058,7 +21064,7 @@
       <c r="N311" s="15"/>
       <c r="O311" s="22"/>
     </row>
-    <row r="312" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" s="19" t="s">
         <v>938</v>
       </c>
@@ -21101,7 +21107,7 @@
       <c r="N312" s="13"/>
       <c r="O312" s="20"/>
     </row>
-    <row r="313" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" s="21" t="s">
         <v>939</v>
       </c>
@@ -21144,7 +21150,7 @@
       <c r="N313" s="15"/>
       <c r="O313" s="22"/>
     </row>
-    <row r="314" spans="1:15" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:15" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" s="19" t="s">
         <v>940</v>
       </c>
@@ -21189,7 +21195,7 @@
       </c>
       <c r="O314" s="20"/>
     </row>
-    <row r="315" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" s="21" t="s">
         <v>942</v>
       </c>
@@ -21232,7 +21238,7 @@
       <c r="N315" s="15"/>
       <c r="O315" s="22"/>
     </row>
-    <row r="316" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" s="19" t="s">
         <v>944</v>
       </c>
@@ -21275,7 +21281,7 @@
       <c r="N316" s="13"/>
       <c r="O316" s="20"/>
     </row>
-    <row r="317" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" s="21" t="s">
         <v>946</v>
       </c>
@@ -21318,7 +21324,7 @@
       <c r="N317" s="15"/>
       <c r="O317" s="22"/>
     </row>
-    <row r="318" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" s="19" t="s">
         <v>948</v>
       </c>
@@ -21361,7 +21367,7 @@
       <c r="N318" s="13"/>
       <c r="O318" s="20"/>
     </row>
-    <row r="319" spans="1:15" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:15" ht="187.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="21" t="s">
         <v>949</v>
       </c>
@@ -21406,7 +21412,7 @@
       </c>
       <c r="O319" s="22"/>
     </row>
-    <row r="320" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="19" t="s">
         <v>951</v>
       </c>
@@ -21449,7 +21455,7 @@
       <c r="N320" s="13"/>
       <c r="O320" s="20"/>
     </row>
-    <row r="321" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" s="21" t="s">
         <v>953</v>
       </c>
@@ -21494,7 +21500,7 @@
       </c>
       <c r="O321" s="22"/>
     </row>
-    <row r="322" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" s="19" t="s">
         <v>962</v>
       </c>
@@ -21537,7 +21543,7 @@
       <c r="N322" s="13"/>
       <c r="O322" s="20"/>
     </row>
-    <row r="323" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" s="21" t="s">
         <v>964</v>
       </c>
@@ -21580,7 +21586,7 @@
       <c r="N323" s="15"/>
       <c r="O323" s="22"/>
     </row>
-    <row r="324" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" s="19" t="s">
         <v>965</v>
       </c>
@@ -21623,7 +21629,7 @@
       <c r="N324" s="13"/>
       <c r="O324" s="20"/>
     </row>
-    <row r="325" spans="1:15" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:15" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" s="21" t="s">
         <v>967</v>
       </c>
@@ -21666,7 +21672,7 @@
       <c r="N325" s="15"/>
       <c r="O325" s="22"/>
     </row>
-    <row r="326" spans="1:15" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:15" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" s="19" t="s">
         <v>971</v>
       </c>
@@ -21711,7 +21717,7 @@
       </c>
       <c r="O326" s="20"/>
     </row>
-    <row r="327" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" s="21" t="s">
         <v>973</v>
       </c>
@@ -21754,7 +21760,7 @@
       <c r="N327" s="15"/>
       <c r="O327" s="22"/>
     </row>
-    <row r="328" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" s="19" t="s">
         <v>977</v>
       </c>
@@ -21837,10 +21843,12 @@
       <c r="M329" s="15" t="s">
         <v>2300</v>
       </c>
-      <c r="N329" s="15"/>
+      <c r="N329" s="15" t="s">
+        <v>2301</v>
+      </c>
       <c r="O329" s="22"/>
     </row>
-    <row r="330" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" s="19" t="s">
         <v>980</v>
       </c>
@@ -21885,7 +21893,7 @@
       </c>
       <c r="O330" s="20"/>
     </row>
-    <row r="331" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" s="21" t="s">
         <v>981</v>
       </c>
@@ -21930,7 +21938,7 @@
       </c>
       <c r="O331" s="22"/>
     </row>
-    <row r="332" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" s="19" t="s">
         <v>985</v>
       </c>
@@ -21973,7 +21981,7 @@
       <c r="N332" s="13"/>
       <c r="O332" s="20"/>
     </row>
-    <row r="333" spans="1:15" ht="216" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:15" ht="216" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" s="21" t="s">
         <v>987</v>
       </c>
@@ -22016,7 +22024,7 @@
       <c r="N333" s="15"/>
       <c r="O333" s="22"/>
     </row>
-    <row r="334" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" s="19" t="s">
         <v>988</v>
       </c>
@@ -22059,7 +22067,7 @@
       <c r="N334" s="13"/>
       <c r="O334" s="20"/>
     </row>
-    <row r="335" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" s="21" t="s">
         <v>990</v>
       </c>
@@ -22104,7 +22112,7 @@
       </c>
       <c r="O335" s="22"/>
     </row>
-    <row r="336" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" s="19" t="s">
         <v>996</v>
       </c>
@@ -22147,7 +22155,7 @@
       <c r="N336" s="13"/>
       <c r="O336" s="20"/>
     </row>
-    <row r="337" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" s="21" t="s">
         <v>998</v>
       </c>
@@ -22190,7 +22198,7 @@
       <c r="N337" s="15"/>
       <c r="O337" s="22"/>
     </row>
-    <row r="338" spans="1:15" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:15" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" s="19" t="s">
         <v>1002</v>
       </c>
@@ -22233,7 +22241,7 @@
       <c r="N338" s="13"/>
       <c r="O338" s="20"/>
     </row>
-    <row r="339" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" s="21" t="s">
         <v>1004</v>
       </c>
@@ -22276,7 +22284,7 @@
       <c r="N339" s="15"/>
       <c r="O339" s="22"/>
     </row>
-    <row r="340" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" s="19" t="s">
         <v>1006</v>
       </c>
@@ -22319,7 +22327,7 @@
       <c r="N340" s="13"/>
       <c r="O340" s="20"/>
     </row>
-    <row r="341" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" s="21" t="s">
         <v>1008</v>
       </c>
@@ -22362,7 +22370,7 @@
       <c r="N341" s="15"/>
       <c r="O341" s="22"/>
     </row>
-    <row r="342" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" s="19" t="s">
         <v>1011</v>
       </c>
@@ -22405,7 +22413,7 @@
       <c r="N342" s="13"/>
       <c r="O342" s="20"/>
     </row>
-    <row r="343" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" s="21" t="s">
         <v>1013</v>
       </c>
@@ -22448,7 +22456,7 @@
       <c r="N343" s="15"/>
       <c r="O343" s="22"/>
     </row>
-    <row r="344" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" s="19" t="s">
         <v>1016</v>
       </c>
@@ -22493,7 +22501,7 @@
       </c>
       <c r="O344" s="20"/>
     </row>
-    <row r="345" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" s="21" t="s">
         <v>1019</v>
       </c>
@@ -22536,7 +22544,7 @@
       <c r="N345" s="15"/>
       <c r="O345" s="22"/>
     </row>
-    <row r="346" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" s="19" t="s">
         <v>1023</v>
       </c>
@@ -22579,7 +22587,7 @@
       <c r="N346" s="13"/>
       <c r="O346" s="20"/>
     </row>
-    <row r="347" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" s="21" t="s">
         <v>1025</v>
       </c>
@@ -22622,7 +22630,7 @@
       <c r="N347" s="15"/>
       <c r="O347" s="22"/>
     </row>
-    <row r="348" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" s="19" t="s">
         <v>1028</v>
       </c>
@@ -22665,7 +22673,7 @@
       <c r="N348" s="13"/>
       <c r="O348" s="20"/>
     </row>
-    <row r="349" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" s="21" t="s">
         <v>1030</v>
       </c>
@@ -22708,7 +22716,7 @@
       <c r="N349" s="15"/>
       <c r="O349" s="22"/>
     </row>
-    <row r="350" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" s="19" t="s">
         <v>1032</v>
       </c>
@@ -22751,7 +22759,7 @@
       <c r="N350" s="13"/>
       <c r="O350" s="20"/>
     </row>
-    <row r="351" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" s="21" t="s">
         <v>1036</v>
       </c>
@@ -22794,7 +22802,7 @@
       <c r="N351" s="15"/>
       <c r="O351" s="22"/>
     </row>
-    <row r="352" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" s="19" t="s">
         <v>1037</v>
       </c>
@@ -22837,7 +22845,7 @@
       <c r="N352" s="13"/>
       <c r="O352" s="20"/>
     </row>
-    <row r="353" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" s="21" t="s">
         <v>1041</v>
       </c>
@@ -22882,7 +22890,7 @@
       </c>
       <c r="O353" s="22"/>
     </row>
-    <row r="354" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" s="19" t="s">
         <v>1045</v>
       </c>
@@ -22927,7 +22935,7 @@
       </c>
       <c r="O354" s="20"/>
     </row>
-    <row r="355" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" s="21" t="s">
         <v>1047</v>
       </c>
@@ -22970,7 +22978,7 @@
       <c r="N355" s="15"/>
       <c r="O355" s="22"/>
     </row>
-    <row r="356" spans="1:15" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:15" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" s="19" t="s">
         <v>1050</v>
       </c>
@@ -23013,7 +23021,7 @@
       <c r="N356" s="13"/>
       <c r="O356" s="20"/>
     </row>
-    <row r="357" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" s="21" t="s">
         <v>1052</v>
       </c>
@@ -23056,7 +23064,7 @@
       <c r="N357" s="15"/>
       <c r="O357" s="22"/>
     </row>
-    <row r="358" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" s="19" t="s">
         <v>1054</v>
       </c>
@@ -23099,7 +23107,7 @@
       <c r="N358" s="13"/>
       <c r="O358" s="20"/>
     </row>
-    <row r="359" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" s="21" t="s">
         <v>1055</v>
       </c>
@@ -23144,7 +23152,7 @@
       </c>
       <c r="O359" s="22"/>
     </row>
-    <row r="360" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" s="19" t="s">
         <v>1057</v>
       </c>
@@ -23189,7 +23197,7 @@
       </c>
       <c r="O360" s="20"/>
     </row>
-    <row r="361" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" s="21" t="s">
         <v>1061</v>
       </c>
@@ -23232,7 +23240,7 @@
       <c r="N361" s="15"/>
       <c r="O361" s="22"/>
     </row>
-    <row r="362" spans="1:15" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:15" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" s="19" t="s">
         <v>1063</v>
       </c>
@@ -23275,7 +23283,7 @@
       <c r="N362" s="13"/>
       <c r="O362" s="20"/>
     </row>
-    <row r="363" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" s="21" t="s">
         <v>1064</v>
       </c>
@@ -23318,7 +23326,7 @@
       <c r="N363" s="15"/>
       <c r="O363" s="22"/>
     </row>
-    <row r="364" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" s="19" t="s">
         <v>1066</v>
       </c>
@@ -23361,7 +23369,7 @@
       <c r="N364" s="13"/>
       <c r="O364" s="20"/>
     </row>
-    <row r="365" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" s="21" t="s">
         <v>1071</v>
       </c>
@@ -23406,7 +23414,7 @@
       </c>
       <c r="O365" s="22"/>
     </row>
-    <row r="366" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" s="19" t="s">
         <v>1074</v>
       </c>
@@ -23449,7 +23457,7 @@
       <c r="N366" s="13"/>
       <c r="O366" s="20"/>
     </row>
-    <row r="367" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" s="21" t="s">
         <v>1082</v>
       </c>
@@ -23492,7 +23500,7 @@
       <c r="N367" s="15"/>
       <c r="O367" s="22"/>
     </row>
-    <row r="368" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" s="19" t="s">
         <v>1083</v>
       </c>
@@ -23535,7 +23543,7 @@
       <c r="N368" s="13"/>
       <c r="O368" s="20"/>
     </row>
-    <row r="369" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" s="21" t="s">
         <v>1092</v>
       </c>
@@ -23578,7 +23586,7 @@
       <c r="N369" s="15"/>
       <c r="O369" s="22"/>
     </row>
-    <row r="370" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" s="19" t="s">
         <v>1094</v>
       </c>
@@ -23621,7 +23629,7 @@
       <c r="N370" s="13"/>
       <c r="O370" s="20"/>
     </row>
-    <row r="371" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" s="21" t="s">
         <v>1096</v>
       </c>
@@ -23664,7 +23672,7 @@
       <c r="N371" s="15"/>
       <c r="O371" s="22"/>
     </row>
-    <row r="372" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" s="19" t="s">
         <v>1101</v>
       </c>
@@ -23707,7 +23715,7 @@
       <c r="N372" s="13"/>
       <c r="O372" s="20"/>
     </row>
-    <row r="373" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" s="21" t="s">
         <v>1105</v>
       </c>
@@ -23752,7 +23760,7 @@
       </c>
       <c r="O373" s="22"/>
     </row>
-    <row r="374" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" s="19" t="s">
         <v>1106</v>
       </c>
@@ -23795,7 +23803,7 @@
       <c r="N374" s="13"/>
       <c r="O374" s="20"/>
     </row>
-    <row r="375" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" s="21" t="s">
         <v>1112</v>
       </c>
@@ -23838,7 +23846,7 @@
       <c r="N375" s="15"/>
       <c r="O375" s="22"/>
     </row>
-    <row r="376" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" s="19" t="s">
         <v>1116</v>
       </c>
@@ -23881,7 +23889,7 @@
       <c r="N376" s="13"/>
       <c r="O376" s="20"/>
     </row>
-    <row r="377" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" s="21" t="s">
         <v>1119</v>
       </c>
@@ -23926,7 +23934,7 @@
       </c>
       <c r="O377" s="22"/>
     </row>
-    <row r="378" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" s="19" t="s">
         <v>1121</v>
       </c>
@@ -23969,7 +23977,7 @@
       <c r="N378" s="13"/>
       <c r="O378" s="20"/>
     </row>
-    <row r="379" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" s="21" t="s">
         <v>1123</v>
       </c>
@@ -24014,7 +24022,7 @@
       </c>
       <c r="O379" s="22"/>
     </row>
-    <row r="380" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" s="19" t="s">
         <v>1128</v>
       </c>
@@ -24057,7 +24065,7 @@
       <c r="N380" s="13"/>
       <c r="O380" s="20"/>
     </row>
-    <row r="381" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" s="21" t="s">
         <v>1131</v>
       </c>
@@ -24102,7 +24110,7 @@
       </c>
       <c r="O381" s="22"/>
     </row>
-    <row r="382" spans="1:15" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:15" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" s="19" t="s">
         <v>1132</v>
       </c>
@@ -24145,7 +24153,7 @@
       <c r="N382" s="13"/>
       <c r="O382" s="20"/>
     </row>
-    <row r="383" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" s="21" t="s">
         <v>1135</v>
       </c>
@@ -24188,7 +24196,7 @@
       <c r="N383" s="15"/>
       <c r="O383" s="22"/>
     </row>
-    <row r="384" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" s="19" t="s">
         <v>1137</v>
       </c>
@@ -24231,7 +24239,7 @@
       <c r="N384" s="13"/>
       <c r="O384" s="20"/>
     </row>
-    <row r="385" spans="1:15" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:15" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" s="21" t="s">
         <v>1142</v>
       </c>
@@ -24274,7 +24282,7 @@
       <c r="N385" s="15"/>
       <c r="O385" s="22"/>
     </row>
-    <row r="386" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" s="19" t="s">
         <v>1143</v>
       </c>
@@ -24319,7 +24327,7 @@
       </c>
       <c r="O386" s="20"/>
     </row>
-    <row r="387" spans="1:15" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:15" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" s="21" t="s">
         <v>1145</v>
       </c>
@@ -24362,7 +24370,7 @@
       <c r="N387" s="15"/>
       <c r="O387" s="22"/>
     </row>
-    <row r="388" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" s="19" t="s">
         <v>1150</v>
       </c>
@@ -24405,7 +24413,7 @@
       <c r="N388" s="13"/>
       <c r="O388" s="20"/>
     </row>
-    <row r="389" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" s="21" t="s">
         <v>1151</v>
       </c>
@@ -24448,7 +24456,7 @@
       <c r="N389" s="15"/>
       <c r="O389" s="22"/>
     </row>
-    <row r="390" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" s="19" t="s">
         <v>1153</v>
       </c>
@@ -24491,7 +24499,7 @@
       <c r="N390" s="13"/>
       <c r="O390" s="20"/>
     </row>
-    <row r="391" spans="1:15" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:15" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" s="21" t="s">
         <v>1154</v>
       </c>
@@ -24534,7 +24542,7 @@
       <c r="N391" s="15"/>
       <c r="O391" s="22"/>
     </row>
-    <row r="392" spans="1:15" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:15" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" s="19" t="s">
         <v>1157</v>
       </c>
@@ -24579,7 +24587,7 @@
       </c>
       <c r="O392" s="20"/>
     </row>
-    <row r="393" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" s="21" t="s">
         <v>1158</v>
       </c>
@@ -24622,7 +24630,7 @@
       <c r="N393" s="15"/>
       <c r="O393" s="22"/>
     </row>
-    <row r="394" spans="1:15" ht="216" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:15" ht="216" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" s="19" t="s">
         <v>1159</v>
       </c>
@@ -24665,7 +24673,7 @@
       <c r="N394" s="13"/>
       <c r="O394" s="20"/>
     </row>
-    <row r="395" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" s="21" t="s">
         <v>1162</v>
       </c>
@@ -24710,7 +24718,7 @@
       </c>
       <c r="O395" s="22"/>
     </row>
-    <row r="396" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" s="19" t="s">
         <v>1164</v>
       </c>
@@ -24753,7 +24761,7 @@
       <c r="N396" s="13"/>
       <c r="O396" s="20"/>
     </row>
-    <row r="397" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" s="21" t="s">
         <v>1165</v>
       </c>
@@ -24796,7 +24804,7 @@
       <c r="N397" s="15"/>
       <c r="O397" s="22"/>
     </row>
-    <row r="398" spans="1:15" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:15" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" s="19" t="s">
         <v>1167</v>
       </c>
@@ -24839,7 +24847,7 @@
       <c r="N398" s="13"/>
       <c r="O398" s="20"/>
     </row>
-    <row r="399" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" s="21" t="s">
         <v>1169</v>
       </c>
@@ -24882,7 +24890,7 @@
       <c r="N399" s="15"/>
       <c r="O399" s="22"/>
     </row>
-    <row r="400" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" s="19" t="s">
         <v>1173</v>
       </c>
@@ -24925,7 +24933,7 @@
       <c r="N400" s="13"/>
       <c r="O400" s="20"/>
     </row>
-    <row r="401" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" s="21" t="s">
         <v>1175</v>
       </c>
@@ -24968,7 +24976,7 @@
       <c r="N401" s="15"/>
       <c r="O401" s="22"/>
     </row>
-    <row r="402" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" s="19" t="s">
         <v>1177</v>
       </c>
@@ -25011,7 +25019,7 @@
       <c r="N402" s="13"/>
       <c r="O402" s="20"/>
     </row>
-    <row r="403" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" s="21" t="s">
         <v>1178</v>
       </c>
@@ -25054,7 +25062,7 @@
       <c r="N403" s="15"/>
       <c r="O403" s="22"/>
     </row>
-    <row r="404" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" s="19" t="s">
         <v>1180</v>
       </c>
@@ -25099,7 +25107,7 @@
       </c>
       <c r="O404" s="20"/>
     </row>
-    <row r="405" spans="1:15" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:15" ht="302.39999999999998" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" s="21" t="s">
         <v>1182</v>
       </c>
@@ -25144,7 +25152,7 @@
       </c>
       <c r="O405" s="22"/>
     </row>
-    <row r="406" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" s="19" t="s">
         <v>1190</v>
       </c>
@@ -25189,7 +25197,7 @@
       </c>
       <c r="O406" s="20"/>
     </row>
-    <row r="407" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407" s="21" t="s">
         <v>1192</v>
       </c>
@@ -25232,7 +25240,7 @@
       <c r="N407" s="15"/>
       <c r="O407" s="22"/>
     </row>
-    <row r="408" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408" s="19" t="s">
         <v>1193</v>
       </c>
@@ -25277,7 +25285,7 @@
       </c>
       <c r="O408" s="20"/>
     </row>
-    <row r="409" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" s="21" t="s">
         <v>1195</v>
       </c>
@@ -25320,7 +25328,7 @@
       <c r="N409" s="15"/>
       <c r="O409" s="22"/>
     </row>
-    <row r="410" spans="1:15" ht="273.60000000000002" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:15" ht="273.60000000000002" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" s="19" t="s">
         <v>1200</v>
       </c>
@@ -25363,7 +25371,7 @@
       <c r="N410" s="13"/>
       <c r="O410" s="20"/>
     </row>
-    <row r="411" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" s="21" t="s">
         <v>1203</v>
       </c>
@@ -25406,7 +25414,7 @@
       <c r="N411" s="15"/>
       <c r="O411" s="22"/>
     </row>
-    <row r="412" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" s="19" t="s">
         <v>1210</v>
       </c>
@@ -25451,7 +25459,7 @@
       </c>
       <c r="O412" s="20"/>
     </row>
-    <row r="413" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" s="21" t="s">
         <v>1214</v>
       </c>
@@ -25494,7 +25502,7 @@
       <c r="N413" s="15"/>
       <c r="O413" s="22"/>
     </row>
-    <row r="414" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" s="19" t="s">
         <v>1220</v>
       </c>
@@ -25539,7 +25547,7 @@
       </c>
       <c r="O414" s="20"/>
     </row>
-    <row r="415" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" s="21" t="s">
         <v>1221</v>
       </c>
@@ -25582,7 +25590,7 @@
       <c r="N415" s="15"/>
       <c r="O415" s="22"/>
     </row>
-    <row r="416" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" s="19" t="s">
         <v>1226</v>
       </c>
@@ -25625,7 +25633,7 @@
       <c r="N416" s="13"/>
       <c r="O416" s="20"/>
     </row>
-    <row r="417" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" s="21" t="s">
         <v>1228</v>
       </c>
@@ -25668,7 +25676,7 @@
       <c r="N417" s="15"/>
       <c r="O417" s="22"/>
     </row>
-    <row r="418" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" s="19" t="s">
         <v>1230</v>
       </c>
@@ -25711,7 +25719,7 @@
       <c r="N418" s="13"/>
       <c r="O418" s="20"/>
     </row>
-    <row r="419" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" s="21" t="s">
         <v>1234</v>
       </c>
@@ -25754,7 +25762,7 @@
       <c r="N419" s="15"/>
       <c r="O419" s="22"/>
     </row>
-    <row r="420" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" s="19" t="s">
         <v>1236</v>
       </c>
@@ -25797,7 +25805,7 @@
       <c r="N420" s="13"/>
       <c r="O420" s="20"/>
     </row>
-    <row r="421" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" s="21" t="s">
         <v>1237</v>
       </c>
@@ -25840,7 +25848,7 @@
       <c r="N421" s="15"/>
       <c r="O421" s="22"/>
     </row>
-    <row r="422" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" s="19" t="s">
         <v>1241</v>
       </c>
@@ -25883,7 +25891,7 @@
       <c r="N422" s="13"/>
       <c r="O422" s="20"/>
     </row>
-    <row r="423" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" s="21" t="s">
         <v>1244</v>
       </c>
@@ -25926,7 +25934,7 @@
       <c r="N423" s="15"/>
       <c r="O423" s="22"/>
     </row>
-    <row r="424" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" s="19" t="s">
         <v>1248</v>
       </c>
@@ -25971,7 +25979,7 @@
       </c>
       <c r="O424" s="20"/>
     </row>
-    <row r="425" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" s="21" t="s">
         <v>1251</v>
       </c>
@@ -26014,7 +26022,7 @@
       <c r="N425" s="15"/>
       <c r="O425" s="22"/>
     </row>
-    <row r="426" spans="1:15" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:15" ht="316.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" s="19" t="s">
         <v>1252</v>
       </c>
@@ -26057,7 +26065,7 @@
       <c r="N426" s="13"/>
       <c r="O426" s="20"/>
     </row>
-    <row r="427" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" s="21" t="s">
         <v>1253</v>
       </c>
@@ -26102,7 +26110,7 @@
       </c>
       <c r="O427" s="22"/>
     </row>
-    <row r="428" spans="1:15" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:15" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" s="19" t="s">
         <v>1255</v>
       </c>
@@ -26147,7 +26155,7 @@
       </c>
       <c r="O428" s="20"/>
     </row>
-    <row r="429" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" s="21" t="s">
         <v>1256</v>
       </c>
@@ -26190,7 +26198,7 @@
       <c r="N429" s="15"/>
       <c r="O429" s="22"/>
     </row>
-    <row r="430" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" s="19" t="s">
         <v>1258</v>
       </c>
@@ -26235,7 +26243,7 @@
       </c>
       <c r="O430" s="20"/>
     </row>
-    <row r="431" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" s="21" t="s">
         <v>1259</v>
       </c>
@@ -26280,7 +26288,7 @@
       </c>
       <c r="O431" s="22"/>
     </row>
-    <row r="432" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" s="19" t="s">
         <v>1263</v>
       </c>
@@ -26323,7 +26331,7 @@
       <c r="N432" s="13"/>
       <c r="O432" s="20"/>
     </row>
-    <row r="433" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" s="21" t="s">
         <v>1266</v>
       </c>
@@ -26366,7 +26374,7 @@
       <c r="N433" s="15"/>
       <c r="O433" s="22"/>
     </row>
-    <row r="434" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" s="19" t="s">
         <v>1269</v>
       </c>
@@ -26409,7 +26417,7 @@
       <c r="N434" s="13"/>
       <c r="O434" s="20"/>
     </row>
-    <row r="435" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" s="21" t="s">
         <v>1273</v>
       </c>
@@ -26454,7 +26462,7 @@
       </c>
       <c r="O435" s="22"/>
     </row>
-    <row r="436" spans="1:15" ht="216" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:15" ht="216" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436" s="19" t="s">
         <v>1282</v>
       </c>
@@ -26497,7 +26505,7 @@
       <c r="N436" s="13"/>
       <c r="O436" s="20"/>
     </row>
-    <row r="437" spans="1:15" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:15" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437" s="21" t="s">
         <v>1284</v>
       </c>
@@ -26540,7 +26548,7 @@
       <c r="N437" s="15"/>
       <c r="O437" s="22"/>
     </row>
-    <row r="438" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" s="19" t="s">
         <v>1292</v>
       </c>
@@ -26583,7 +26591,7 @@
       <c r="N438" s="13"/>
       <c r="O438" s="20"/>
     </row>
-    <row r="439" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" s="21" t="s">
         <v>1293</v>
       </c>
@@ -26628,7 +26636,7 @@
       </c>
       <c r="O439" s="22"/>
     </row>
-    <row r="440" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" s="19" t="s">
         <v>1300</v>
       </c>
@@ -26671,7 +26679,7 @@
       <c r="N440" s="13"/>
       <c r="O440" s="20"/>
     </row>
-    <row r="441" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441" s="21" t="s">
         <v>1302</v>
       </c>
@@ -26714,7 +26722,7 @@
       <c r="N441" s="15"/>
       <c r="O441" s="22"/>
     </row>
-    <row r="442" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442" s="19" t="s">
         <v>1306</v>
       </c>
@@ -26757,7 +26765,7 @@
       <c r="N442" s="13"/>
       <c r="O442" s="20"/>
     </row>
-    <row r="443" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443" s="21" t="s">
         <v>1307</v>
       </c>
@@ -26802,7 +26810,7 @@
       </c>
       <c r="O443" s="22"/>
     </row>
-    <row r="444" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" s="19" t="s">
         <v>1315</v>
       </c>
@@ -26847,7 +26855,7 @@
       </c>
       <c r="O444" s="20"/>
     </row>
-    <row r="445" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445" s="21" t="s">
         <v>1317</v>
       </c>
@@ -26890,7 +26898,7 @@
       <c r="N445" s="15"/>
       <c r="O445" s="22"/>
     </row>
-    <row r="446" spans="1:15" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:15" ht="187.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" s="19" t="s">
         <v>1318</v>
       </c>
@@ -26933,7 +26941,7 @@
       <c r="N446" s="13"/>
       <c r="O446" s="20"/>
     </row>
-    <row r="447" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" s="21" t="s">
         <v>1320</v>
       </c>
@@ -26976,7 +26984,7 @@
       <c r="N447" s="15"/>
       <c r="O447" s="22"/>
     </row>
-    <row r="448" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" s="19" t="s">
         <v>1322</v>
       </c>
@@ -27019,7 +27027,7 @@
       <c r="N448" s="13"/>
       <c r="O448" s="20"/>
     </row>
-    <row r="449" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449" s="21" t="s">
         <v>1324</v>
       </c>
@@ -27062,7 +27070,7 @@
       <c r="N449" s="15"/>
       <c r="O449" s="22"/>
     </row>
-    <row r="450" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" s="19" t="s">
         <v>1327</v>
       </c>
@@ -27107,7 +27115,7 @@
       </c>
       <c r="O450" s="20"/>
     </row>
-    <row r="451" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451" s="21" t="s">
         <v>1330</v>
       </c>
@@ -27150,7 +27158,7 @@
       <c r="N451" s="15"/>
       <c r="O451" s="22"/>
     </row>
-    <row r="452" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452" s="19" t="s">
         <v>1331</v>
       </c>
@@ -27195,7 +27203,7 @@
       </c>
       <c r="O452" s="20"/>
     </row>
-    <row r="453" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" s="21" t="s">
         <v>1335</v>
       </c>
@@ -27238,7 +27246,7 @@
       <c r="N453" s="15"/>
       <c r="O453" s="22"/>
     </row>
-    <row r="454" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454" s="19" t="s">
         <v>1338</v>
       </c>
@@ -27281,7 +27289,7 @@
       <c r="N454" s="13"/>
       <c r="O454" s="20"/>
     </row>
-    <row r="455" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455" s="21" t="s">
         <v>1351</v>
       </c>
@@ -27324,7 +27332,7 @@
       <c r="N455" s="15"/>
       <c r="O455" s="22"/>
     </row>
-    <row r="456" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" s="19" t="s">
         <v>1357</v>
       </c>
@@ -27367,7 +27375,7 @@
       <c r="N456" s="13"/>
       <c r="O456" s="20"/>
     </row>
-    <row r="457" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" s="21" t="s">
         <v>1360</v>
       </c>
@@ -27412,7 +27420,7 @@
       </c>
       <c r="O457" s="22"/>
     </row>
-    <row r="458" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458" s="19" t="s">
         <v>1362</v>
       </c>
@@ -27455,7 +27463,7 @@
       <c r="N458" s="13"/>
       <c r="O458" s="20"/>
     </row>
-    <row r="459" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" s="21" t="s">
         <v>1364</v>
       </c>
@@ -27498,7 +27506,7 @@
       <c r="N459" s="15"/>
       <c r="O459" s="22"/>
     </row>
-    <row r="460" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" s="19" t="s">
         <v>1366</v>
       </c>
@@ -27543,7 +27551,7 @@
       </c>
       <c r="O460" s="20"/>
     </row>
-    <row r="461" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" s="21" t="s">
         <v>1368</v>
       </c>
@@ -27586,7 +27594,7 @@
       <c r="N461" s="15"/>
       <c r="O461" s="22"/>
     </row>
-    <row r="462" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" s="19" t="s">
         <v>1371</v>
       </c>
@@ -27629,7 +27637,7 @@
       <c r="N462" s="13"/>
       <c r="O462" s="20"/>
     </row>
-    <row r="463" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" s="21" t="s">
         <v>1373</v>
       </c>
@@ -27674,7 +27682,7 @@
       </c>
       <c r="O463" s="22"/>
     </row>
-    <row r="464" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" s="19" t="s">
         <v>1374</v>
       </c>
@@ -27717,7 +27725,7 @@
       <c r="N464" s="13"/>
       <c r="O464" s="20"/>
     </row>
-    <row r="465" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" s="21" t="s">
         <v>1384</v>
       </c>
@@ -27760,7 +27768,7 @@
       <c r="N465" s="15"/>
       <c r="O465" s="22"/>
     </row>
-    <row r="466" spans="1:15" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:15" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" s="19" t="s">
         <v>1387</v>
       </c>
@@ -27803,7 +27811,7 @@
       <c r="N466" s="13"/>
       <c r="O466" s="20"/>
     </row>
-    <row r="467" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" s="21" t="s">
         <v>1389</v>
       </c>
@@ -27846,7 +27854,7 @@
       <c r="N467" s="15"/>
       <c r="O467" s="22"/>
     </row>
-    <row r="468" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" s="19" t="s">
         <v>1390</v>
       </c>
@@ -27889,7 +27897,7 @@
       <c r="N468" s="13"/>
       <c r="O468" s="20"/>
     </row>
-    <row r="469" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469" s="21" t="s">
         <v>1392</v>
       </c>
@@ -27932,7 +27940,7 @@
       <c r="N469" s="15"/>
       <c r="O469" s="22"/>
     </row>
-    <row r="470" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470" s="19" t="s">
         <v>1395</v>
       </c>
@@ -27975,7 +27983,7 @@
       <c r="N470" s="13"/>
       <c r="O470" s="20"/>
     </row>
-    <row r="471" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471" s="21" t="s">
         <v>1397</v>
       </c>
@@ -28018,7 +28026,7 @@
       <c r="N471" s="15"/>
       <c r="O471" s="22"/>
     </row>
-    <row r="472" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472" s="19" t="s">
         <v>1399</v>
       </c>
@@ -28061,7 +28069,7 @@
       <c r="N472" s="13"/>
       <c r="O472" s="20"/>
     </row>
-    <row r="473" spans="1:15" ht="144" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:15" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473" s="21" t="s">
         <v>1400</v>
       </c>
@@ -28106,7 +28114,7 @@
       </c>
       <c r="O473" s="22"/>
     </row>
-    <row r="474" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474" s="19" t="s">
         <v>1401</v>
       </c>
@@ -28151,7 +28159,7 @@
       </c>
       <c r="O474" s="20"/>
     </row>
-    <row r="475" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475" s="21" t="s">
         <v>1403</v>
       </c>
@@ -28196,7 +28204,7 @@
       </c>
       <c r="O475" s="22"/>
     </row>
-    <row r="476" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476" s="19" t="s">
         <v>1405</v>
       </c>
@@ -28239,7 +28247,7 @@
       <c r="N476" s="13"/>
       <c r="O476" s="20"/>
     </row>
-    <row r="477" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477" s="21" t="s">
         <v>1407</v>
       </c>
@@ -28282,7 +28290,7 @@
       <c r="N477" s="15"/>
       <c r="O477" s="22"/>
     </row>
-    <row r="478" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478" s="19" t="s">
         <v>1408</v>
       </c>
@@ -28325,7 +28333,7 @@
       <c r="N478" s="13"/>
       <c r="O478" s="20"/>
     </row>
-    <row r="479" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479" s="21" t="s">
         <v>1410</v>
       </c>
@@ -28370,7 +28378,7 @@
       </c>
       <c r="O479" s="22"/>
     </row>
-    <row r="480" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480" s="19" t="s">
         <v>1412</v>
       </c>
@@ -28413,7 +28421,7 @@
       <c r="N480" s="13"/>
       <c r="O480" s="20"/>
     </row>
-    <row r="481" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481" s="21" t="s">
         <v>1414</v>
       </c>
@@ -28458,7 +28466,7 @@
       </c>
       <c r="O481" s="22"/>
     </row>
-    <row r="482" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482" s="19" t="s">
         <v>1416</v>
       </c>
@@ -28501,7 +28509,7 @@
       <c r="N482" s="13"/>
       <c r="O482" s="20"/>
     </row>
-    <row r="483" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483" s="21" t="s">
         <v>1418</v>
       </c>
@@ -28544,7 +28552,7 @@
       <c r="N483" s="15"/>
       <c r="O483" s="22"/>
     </row>
-    <row r="484" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484" s="19" t="s">
         <v>1420</v>
       </c>
@@ -28587,7 +28595,7 @@
       <c r="N484" s="13"/>
       <c r="O484" s="20"/>
     </row>
-    <row r="485" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" s="21" t="s">
         <v>1423</v>
       </c>
@@ -28630,7 +28638,7 @@
       <c r="N485" s="15"/>
       <c r="O485" s="22"/>
     </row>
-    <row r="486" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" s="19" t="s">
         <v>1428</v>
       </c>
@@ -28673,7 +28681,7 @@
       <c r="N486" s="13"/>
       <c r="O486" s="20"/>
     </row>
-    <row r="487" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487" s="21" t="s">
         <v>1429</v>
       </c>
@@ -28716,7 +28724,7 @@
       <c r="N487" s="15"/>
       <c r="O487" s="22"/>
     </row>
-    <row r="488" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488" s="19" t="s">
         <v>1431</v>
       </c>
@@ -28759,7 +28767,7 @@
       <c r="N488" s="13"/>
       <c r="O488" s="20"/>
     </row>
-    <row r="489" spans="1:15" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:15" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489" s="21" t="s">
         <v>1437</v>
       </c>
@@ -28802,7 +28810,7 @@
       <c r="N489" s="15"/>
       <c r="O489" s="22"/>
     </row>
-    <row r="490" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490" s="19" t="s">
         <v>1439</v>
       </c>
@@ -28845,7 +28853,7 @@
       <c r="N490" s="13"/>
       <c r="O490" s="20"/>
     </row>
-    <row r="491" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491" s="21" t="s">
         <v>1441</v>
       </c>
@@ -28888,7 +28896,7 @@
       <c r="N491" s="15"/>
       <c r="O491" s="22"/>
     </row>
-    <row r="492" spans="1:15" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:15" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492" s="19" t="s">
         <v>1443</v>
       </c>
@@ -28931,7 +28939,7 @@
       <c r="N492" s="13"/>
       <c r="O492" s="20"/>
     </row>
-    <row r="493" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493" s="21" t="s">
         <v>1447</v>
       </c>
@@ -28974,7 +28982,7 @@
       <c r="N493" s="15"/>
       <c r="O493" s="22"/>
     </row>
-    <row r="494" spans="1:15" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:15" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494" s="19" t="s">
         <v>1451</v>
       </c>
@@ -29017,7 +29025,7 @@
       <c r="N494" s="13"/>
       <c r="O494" s="20"/>
     </row>
-    <row r="495" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A495" s="21" t="s">
         <v>1457</v>
       </c>
@@ -29060,7 +29068,7 @@
       <c r="N495" s="15"/>
       <c r="O495" s="22"/>
     </row>
-    <row r="496" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496" s="19" t="s">
         <v>1460</v>
       </c>
@@ -29103,7 +29111,7 @@
       <c r="N496" s="13"/>
       <c r="O496" s="20"/>
     </row>
-    <row r="497" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A497" s="21" t="s">
         <v>1464</v>
       </c>
@@ -29146,7 +29154,7 @@
       <c r="N497" s="15"/>
       <c r="O497" s="22"/>
     </row>
-    <row r="498" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498" s="19" t="s">
         <v>1465</v>
       </c>
@@ -29189,7 +29197,7 @@
       <c r="N498" s="13"/>
       <c r="O498" s="20"/>
     </row>
-    <row r="499" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499" s="21" t="s">
         <v>1471</v>
       </c>
@@ -29232,7 +29240,7 @@
       <c r="N499" s="15"/>
       <c r="O499" s="22"/>
     </row>
-    <row r="500" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500" s="19" t="s">
         <v>1476</v>
       </c>
@@ -29275,7 +29283,7 @@
       <c r="N500" s="13"/>
       <c r="O500" s="20"/>
     </row>
-    <row r="501" spans="1:15" ht="144" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:15" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501" s="21" t="s">
         <v>1480</v>
       </c>
@@ -29320,7 +29328,7 @@
       </c>
       <c r="O501" s="22"/>
     </row>
-    <row r="502" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502" s="19" t="s">
         <v>1484</v>
       </c>
@@ -29363,7 +29371,7 @@
       <c r="N502" s="13"/>
       <c r="O502" s="20"/>
     </row>
-    <row r="503" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503" s="21" t="s">
         <v>1485</v>
       </c>
@@ -29406,7 +29414,7 @@
       <c r="N503" s="15"/>
       <c r="O503" s="22"/>
     </row>
-    <row r="504" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504" s="19" t="s">
         <v>1486</v>
       </c>
@@ -29449,7 +29457,7 @@
       <c r="N504" s="13"/>
       <c r="O504" s="20"/>
     </row>
-    <row r="505" spans="1:15" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:15" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505" s="21" t="s">
         <v>1487</v>
       </c>
@@ -29492,7 +29500,7 @@
       <c r="N505" s="15"/>
       <c r="O505" s="22"/>
     </row>
-    <row r="506" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506" s="19" t="s">
         <v>1489</v>
       </c>
@@ -29537,7 +29545,7 @@
       </c>
       <c r="O506" s="20"/>
     </row>
-    <row r="507" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507" s="21" t="s">
         <v>1491</v>
       </c>
@@ -29580,7 +29588,7 @@
       <c r="N507" s="15"/>
       <c r="O507" s="22"/>
     </row>
-    <row r="508" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508" s="19" t="s">
         <v>1494</v>
       </c>
@@ -29623,7 +29631,7 @@
       <c r="N508" s="13"/>
       <c r="O508" s="20"/>
     </row>
-    <row r="509" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509" s="21" t="s">
         <v>1496</v>
       </c>
@@ -29666,7 +29674,7 @@
       <c r="N509" s="15"/>
       <c r="O509" s="22"/>
     </row>
-    <row r="510" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510" s="19" t="s">
         <v>1498</v>
       </c>
@@ -29709,7 +29717,7 @@
       <c r="N510" s="13"/>
       <c r="O510" s="20"/>
     </row>
-    <row r="511" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511" s="21" t="s">
         <v>1500</v>
       </c>
@@ -29752,7 +29760,7 @@
       <c r="N511" s="15"/>
       <c r="O511" s="22"/>
     </row>
-    <row r="512" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512" s="19" t="s">
         <v>1502</v>
       </c>
@@ -29795,7 +29803,7 @@
       <c r="N512" s="13"/>
       <c r="O512" s="20"/>
     </row>
-    <row r="513" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513" s="21" t="s">
         <v>1506</v>
       </c>
@@ -29838,7 +29846,7 @@
       <c r="N513" s="15"/>
       <c r="O513" s="22"/>
     </row>
-    <row r="514" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514" s="19" t="s">
         <v>1507</v>
       </c>
@@ -29881,7 +29889,7 @@
       <c r="N514" s="13"/>
       <c r="O514" s="20"/>
     </row>
-    <row r="515" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515" s="21" t="s">
         <v>1508</v>
       </c>
@@ -29924,7 +29932,7 @@
       <c r="N515" s="15"/>
       <c r="O515" s="22"/>
     </row>
-    <row r="516" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516" s="19" t="s">
         <v>1509</v>
       </c>
@@ -29967,7 +29975,7 @@
       <c r="N516" s="13"/>
       <c r="O516" s="20"/>
     </row>
-    <row r="517" spans="1:15" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:15" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517" s="21" t="s">
         <v>1510</v>
       </c>
@@ -30010,7 +30018,7 @@
       <c r="N517" s="15"/>
       <c r="O517" s="22"/>
     </row>
-    <row r="518" spans="1:15" ht="273.60000000000002" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:15" ht="273.60000000000002" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518" s="19" t="s">
         <v>1515</v>
       </c>
@@ -30053,7 +30061,7 @@
       <c r="N518" s="13"/>
       <c r="O518" s="20"/>
     </row>
-    <row r="519" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A519" s="21" t="s">
         <v>1516</v>
       </c>
@@ -30096,7 +30104,7 @@
       <c r="N519" s="15"/>
       <c r="O519" s="22"/>
     </row>
-    <row r="520" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520" s="19" t="s">
         <v>1518</v>
       </c>
@@ -30141,7 +30149,7 @@
       </c>
       <c r="O520" s="20"/>
     </row>
-    <row r="521" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521" s="21" t="s">
         <v>1522</v>
       </c>
@@ -30184,7 +30192,7 @@
       <c r="N521" s="15"/>
       <c r="O521" s="22"/>
     </row>
-    <row r="522" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522" s="19" t="s">
         <v>1523</v>
       </c>
@@ -30227,7 +30235,7 @@
       <c r="N522" s="13"/>
       <c r="O522" s="20"/>
     </row>
-    <row r="523" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523" s="21" t="s">
         <v>1526</v>
       </c>
@@ -30272,7 +30280,7 @@
       </c>
       <c r="O523" s="22"/>
     </row>
-    <row r="524" spans="1:15" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:15" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524" s="19" t="s">
         <v>1527</v>
       </c>
@@ -30315,7 +30323,7 @@
       <c r="N524" s="13"/>
       <c r="O524" s="20"/>
     </row>
-    <row r="525" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525" s="21" t="s">
         <v>1530</v>
       </c>
@@ -30358,7 +30366,7 @@
       <c r="N525" s="15"/>
       <c r="O525" s="22"/>
     </row>
-    <row r="526" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526" s="19" t="s">
         <v>1532</v>
       </c>
@@ -30401,7 +30409,7 @@
       <c r="N526" s="13"/>
       <c r="O526" s="20"/>
     </row>
-    <row r="527" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527" s="21" t="s">
         <v>1533</v>
       </c>
@@ -30446,7 +30454,7 @@
       </c>
       <c r="O527" s="22"/>
     </row>
-    <row r="528" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528" s="19" t="s">
         <v>1534</v>
       </c>
@@ -30489,7 +30497,7 @@
       <c r="N528" s="13"/>
       <c r="O528" s="20"/>
     </row>
-    <row r="529" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529" s="21" t="s">
         <v>1536</v>
       </c>
@@ -30532,7 +30540,7 @@
       <c r="N529" s="15"/>
       <c r="O529" s="22"/>
     </row>
-    <row r="530" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A530" s="19" t="s">
         <v>1541</v>
       </c>
@@ -30575,7 +30583,7 @@
       <c r="N530" s="13"/>
       <c r="O530" s="20"/>
     </row>
-    <row r="531" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A531" s="21" t="s">
         <v>1545</v>
       </c>
@@ -30620,7 +30628,7 @@
       </c>
       <c r="O531" s="22"/>
     </row>
-    <row r="532" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A532" s="19" t="s">
         <v>1551</v>
       </c>
@@ -30663,7 +30671,7 @@
       <c r="N532" s="13"/>
       <c r="O532" s="20"/>
     </row>
-    <row r="533" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533" s="21" t="s">
         <v>1552</v>
       </c>
@@ -30706,7 +30714,7 @@
       <c r="N533" s="15"/>
       <c r="O533" s="22"/>
     </row>
-    <row r="534" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534" s="19" t="s">
         <v>1554</v>
       </c>
@@ -30749,7 +30757,7 @@
       <c r="N534" s="13"/>
       <c r="O534" s="20"/>
     </row>
-    <row r="535" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535" s="21" t="s">
         <v>1557</v>
       </c>
@@ -30792,7 +30800,7 @@
       <c r="N535" s="15"/>
       <c r="O535" s="22"/>
     </row>
-    <row r="536" spans="1:15" ht="144" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:15" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536" s="19" t="s">
         <v>1565</v>
       </c>
@@ -30835,7 +30843,7 @@
       <c r="N536" s="13"/>
       <c r="O536" s="20"/>
     </row>
-    <row r="537" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537" s="21" t="s">
         <v>1567</v>
       </c>
@@ -30880,7 +30888,7 @@
       </c>
       <c r="O537" s="22"/>
     </row>
-    <row r="538" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538" s="19" t="s">
         <v>1569</v>
       </c>
@@ -30923,7 +30931,7 @@
       <c r="N538" s="13"/>
       <c r="O538" s="20"/>
     </row>
-    <row r="539" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539" s="21" t="s">
         <v>1570</v>
       </c>
@@ -30966,7 +30974,7 @@
       <c r="N539" s="15"/>
       <c r="O539" s="22"/>
     </row>
-    <row r="540" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540" s="19" t="s">
         <v>1571</v>
       </c>
@@ -31009,7 +31017,7 @@
       <c r="N540" s="13"/>
       <c r="O540" s="20"/>
     </row>
-    <row r="541" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541" s="21" t="s">
         <v>1574</v>
       </c>
@@ -31052,7 +31060,7 @@
       <c r="N541" s="15"/>
       <c r="O541" s="22"/>
     </row>
-    <row r="542" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A542" s="19" t="s">
         <v>1577</v>
       </c>
@@ -31097,7 +31105,7 @@
       </c>
       <c r="O542" s="20"/>
     </row>
-    <row r="543" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543" s="21" t="s">
         <v>1580</v>
       </c>
@@ -31140,7 +31148,7 @@
       <c r="N543" s="15"/>
       <c r="O543" s="22"/>
     </row>
-    <row r="544" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544" s="19" t="s">
         <v>1583</v>
       </c>
@@ -31183,7 +31191,7 @@
       <c r="N544" s="13"/>
       <c r="O544" s="20"/>
     </row>
-    <row r="545" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545" s="21" t="s">
         <v>1589</v>
       </c>
@@ -31226,7 +31234,7 @@
       <c r="N545" s="15"/>
       <c r="O545" s="22"/>
     </row>
-    <row r="546" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546" s="19" t="s">
         <v>1591</v>
       </c>
@@ -31271,7 +31279,7 @@
       </c>
       <c r="O546" s="20"/>
     </row>
-    <row r="547" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A547" s="21" t="s">
         <v>1593</v>
       </c>
@@ -31314,7 +31322,7 @@
       <c r="N547" s="15"/>
       <c r="O547" s="22"/>
     </row>
-    <row r="548" spans="1:15" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:15" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548" s="19" t="s">
         <v>1594</v>
       </c>
@@ -31359,7 +31367,7 @@
       </c>
       <c r="O548" s="20"/>
     </row>
-    <row r="549" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549" s="21" t="s">
         <v>1596</v>
       </c>
@@ -31402,7 +31410,7 @@
       <c r="N549" s="15"/>
       <c r="O549" s="22"/>
     </row>
-    <row r="550" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550" s="19" t="s">
         <v>1598</v>
       </c>
@@ -31445,7 +31453,7 @@
       <c r="N550" s="13"/>
       <c r="O550" s="20"/>
     </row>
-    <row r="551" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551" s="21" t="s">
         <v>1604</v>
       </c>
@@ -31488,7 +31496,7 @@
       <c r="N551" s="15"/>
       <c r="O551" s="22"/>
     </row>
-    <row r="552" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552" s="19" t="s">
         <v>1608</v>
       </c>
@@ -31531,7 +31539,7 @@
       <c r="N552" s="13"/>
       <c r="O552" s="20"/>
     </row>
-    <row r="553" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553" s="21" t="s">
         <v>1611</v>
       </c>
@@ -31574,7 +31582,7 @@
       <c r="N553" s="15"/>
       <c r="O553" s="22"/>
     </row>
-    <row r="554" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554" s="19" t="s">
         <v>1613</v>
       </c>
@@ -31617,7 +31625,7 @@
       <c r="N554" s="13"/>
       <c r="O554" s="20"/>
     </row>
-    <row r="555" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555" s="21" t="s">
         <v>1615</v>
       </c>
@@ -31660,7 +31668,7 @@
       <c r="N555" s="15"/>
       <c r="O555" s="22"/>
     </row>
-    <row r="556" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556" s="19" t="s">
         <v>1616</v>
       </c>
@@ -31703,7 +31711,7 @@
       <c r="N556" s="13"/>
       <c r="O556" s="20"/>
     </row>
-    <row r="557" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557" s="21" t="s">
         <v>1618</v>
       </c>
@@ -31746,7 +31754,7 @@
       <c r="N557" s="15"/>
       <c r="O557" s="22"/>
     </row>
-    <row r="558" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558" s="19" t="s">
         <v>1620</v>
       </c>
@@ -31789,7 +31797,7 @@
       <c r="N558" s="13"/>
       <c r="O558" s="20"/>
     </row>
-    <row r="559" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559" s="21" t="s">
         <v>1622</v>
       </c>
@@ -31832,7 +31840,7 @@
       <c r="N559" s="15"/>
       <c r="O559" s="22"/>
     </row>
-    <row r="560" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560" s="19" t="s">
         <v>1624</v>
       </c>
@@ -31875,7 +31883,7 @@
       <c r="N560" s="13"/>
       <c r="O560" s="20"/>
     </row>
-    <row r="561" spans="1:15" ht="144" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:15" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561" s="21" t="s">
         <v>1625</v>
       </c>
@@ -31920,7 +31928,7 @@
       </c>
       <c r="O561" s="22"/>
     </row>
-    <row r="562" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A562" s="19" t="s">
         <v>1629</v>
       </c>
@@ -31965,7 +31973,7 @@
       </c>
       <c r="O562" s="20"/>
     </row>
-    <row r="563" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A563" s="21" t="s">
         <v>1631</v>
       </c>
@@ -32008,7 +32016,7 @@
       <c r="N563" s="15"/>
       <c r="O563" s="22"/>
     </row>
-    <row r="564" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564" s="19" t="s">
         <v>1633</v>
       </c>
@@ -32051,7 +32059,7 @@
       <c r="N564" s="13"/>
       <c r="O564" s="20"/>
     </row>
-    <row r="565" spans="1:15" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:15" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A565" s="21" t="s">
         <v>1635</v>
       </c>
@@ -32094,7 +32102,7 @@
       <c r="N565" s="15"/>
       <c r="O565" s="22"/>
     </row>
-    <row r="566" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A566" s="19" t="s">
         <v>1637</v>
       </c>
@@ -32137,7 +32145,7 @@
       <c r="N566" s="13"/>
       <c r="O566" s="20"/>
     </row>
-    <row r="567" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A567" s="21" t="s">
         <v>1638</v>
       </c>
@@ -32182,7 +32190,7 @@
       </c>
       <c r="O567" s="22"/>
     </row>
-    <row r="568" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A568" s="19" t="s">
         <v>1643</v>
       </c>
@@ -32225,7 +32233,7 @@
       <c r="N568" s="13"/>
       <c r="O568" s="20"/>
     </row>
-    <row r="569" spans="1:15" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:15" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569" s="21" t="s">
         <v>1645</v>
       </c>
@@ -32270,7 +32278,7 @@
       </c>
       <c r="O569" s="22"/>
     </row>
-    <row r="570" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570" s="19" t="s">
         <v>1647</v>
       </c>
@@ -32313,7 +32321,7 @@
       <c r="N570" s="13"/>
       <c r="O570" s="20"/>
     </row>
-    <row r="571" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A571" s="21" t="s">
         <v>1658</v>
       </c>
@@ -32356,7 +32364,7 @@
       <c r="N571" s="15"/>
       <c r="O571" s="22"/>
     </row>
-    <row r="572" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A572" s="19" t="s">
         <v>1659</v>
       </c>
@@ -32399,7 +32407,7 @@
       <c r="N572" s="13"/>
       <c r="O572" s="20"/>
     </row>
-    <row r="573" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573" s="21" t="s">
         <v>1660</v>
       </c>
@@ -32442,7 +32450,7 @@
       <c r="N573" s="15"/>
       <c r="O573" s="22"/>
     </row>
-    <row r="574" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574" s="19" t="s">
         <v>1663</v>
       </c>
@@ -32487,7 +32495,7 @@
       </c>
       <c r="O574" s="20"/>
     </row>
-    <row r="575" spans="1:15" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:15" ht="201.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575" s="21" t="s">
         <v>1664</v>
       </c>
@@ -32530,7 +32538,7 @@
       <c r="N575" s="15"/>
       <c r="O575" s="22"/>
     </row>
-    <row r="576" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576" s="19" t="s">
         <v>1666</v>
       </c>
@@ -32573,7 +32581,7 @@
       <c r="N576" s="13"/>
       <c r="O576" s="20"/>
     </row>
-    <row r="577" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A577" s="21" t="s">
         <v>1668</v>
       </c>
@@ -32616,7 +32624,7 @@
       <c r="N577" s="15"/>
       <c r="O577" s="22"/>
     </row>
-    <row r="578" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578" s="19" t="s">
         <v>1669</v>
       </c>
@@ -32659,7 +32667,7 @@
       <c r="N578" s="13"/>
       <c r="O578" s="20"/>
     </row>
-    <row r="579" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A579" s="21" t="s">
         <v>1672</v>
       </c>
@@ -32702,7 +32710,7 @@
       <c r="N579" s="15"/>
       <c r="O579" s="22"/>
     </row>
-    <row r="580" spans="1:15" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:15" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A580" s="19" t="s">
         <v>1678</v>
       </c>
@@ -32745,7 +32753,7 @@
       <c r="N580" s="13"/>
       <c r="O580" s="20"/>
     </row>
-    <row r="581" spans="1:15" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:15" ht="244.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A581" s="21" t="s">
         <v>1681</v>
       </c>
@@ -32788,7 +32796,7 @@
       <c r="N581" s="15"/>
       <c r="O581" s="22"/>
     </row>
-    <row r="582" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A582" s="19" t="s">
         <v>1682</v>
       </c>
@@ -32831,7 +32839,7 @@
       <c r="N582" s="13"/>
       <c r="O582" s="20"/>
     </row>
-    <row r="583" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A583" s="21" t="s">
         <v>1683</v>
       </c>
@@ -32876,7 +32884,7 @@
       </c>
       <c r="O583" s="22"/>
     </row>
-    <row r="584" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A584" s="19" t="s">
         <v>1688</v>
       </c>
@@ -32919,7 +32927,7 @@
       <c r="N584" s="13"/>
       <c r="O584" s="20"/>
     </row>
-    <row r="585" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A585" s="21" t="s">
         <v>1689</v>
       </c>
@@ -32962,7 +32970,7 @@
       <c r="N585" s="15"/>
       <c r="O585" s="22"/>
     </row>
-    <row r="586" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A586" s="19" t="s">
         <v>1692</v>
       </c>
@@ -33005,7 +33013,7 @@
       <c r="N586" s="13"/>
       <c r="O586" s="20"/>
     </row>
-    <row r="587" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A587" s="21" t="s">
         <v>1694</v>
       </c>
@@ -33048,7 +33056,7 @@
       <c r="N587" s="15"/>
       <c r="O587" s="22"/>
     </row>
-    <row r="588" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A588" s="19" t="s">
         <v>1696</v>
       </c>
@@ -33093,7 +33101,7 @@
       </c>
       <c r="O588" s="20"/>
     </row>
-    <row r="589" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A589" s="21" t="s">
         <v>1698</v>
       </c>
@@ -33138,7 +33146,7 @@
       </c>
       <c r="O589" s="22"/>
     </row>
-    <row r="590" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A590" s="19" t="s">
         <v>1699</v>
       </c>
@@ -33183,7 +33191,7 @@
       </c>
       <c r="O590" s="20"/>
     </row>
-    <row r="591" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A591" s="21" t="s">
         <v>1701</v>
       </c>
@@ -33226,7 +33234,7 @@
       <c r="N591" s="15"/>
       <c r="O591" s="22"/>
     </row>
-    <row r="592" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A592" s="19" t="s">
         <v>1705</v>
       </c>
@@ -33269,7 +33277,7 @@
       <c r="N592" s="13"/>
       <c r="O592" s="20"/>
     </row>
-    <row r="593" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A593" s="21" t="s">
         <v>1707</v>
       </c>
@@ -33312,7 +33320,7 @@
       <c r="N593" s="15"/>
       <c r="O593" s="22"/>
     </row>
-    <row r="594" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A594" s="19" t="s">
         <v>1709</v>
       </c>
@@ -33355,7 +33363,7 @@
       <c r="N594" s="13"/>
       <c r="O594" s="20"/>
     </row>
-    <row r="595" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A595" s="21" t="s">
         <v>1712</v>
       </c>
@@ -33398,7 +33406,7 @@
       <c r="N595" s="15"/>
       <c r="O595" s="22"/>
     </row>
-    <row r="596" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A596" s="19" t="s">
         <v>1717</v>
       </c>
@@ -33441,7 +33449,7 @@
       <c r="N596" s="13"/>
       <c r="O596" s="20"/>
     </row>
-    <row r="597" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A597" s="21" t="s">
         <v>1724</v>
       </c>
@@ -33484,7 +33492,7 @@
       <c r="N597" s="15"/>
       <c r="O597" s="22"/>
     </row>
-    <row r="598" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A598" s="19" t="s">
         <v>1727</v>
       </c>
@@ -33527,7 +33535,7 @@
       <c r="N598" s="13"/>
       <c r="O598" s="20"/>
     </row>
-    <row r="599" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A599" s="21" t="s">
         <v>1728</v>
       </c>
@@ -33572,7 +33580,7 @@
       </c>
       <c r="O599" s="22"/>
     </row>
-    <row r="600" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A600" s="19" t="s">
         <v>1730</v>
       </c>
@@ -33617,7 +33625,7 @@
       </c>
       <c r="O600" s="20"/>
     </row>
-    <row r="601" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A601" s="21" t="s">
         <v>1731</v>
       </c>
@@ -33660,7 +33668,7 @@
       <c r="N601" s="15"/>
       <c r="O601" s="22"/>
     </row>
-    <row r="602" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A602" s="19" t="s">
         <v>1735</v>
       </c>
@@ -33703,7 +33711,7 @@
       <c r="N602" s="13"/>
       <c r="O602" s="20"/>
     </row>
-    <row r="603" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A603" s="21" t="s">
         <v>1737</v>
       </c>
@@ -33746,7 +33754,7 @@
       <c r="N603" s="15"/>
       <c r="O603" s="22"/>
     </row>
-    <row r="604" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A604" s="19" t="s">
         <v>1740</v>
       </c>
@@ -33791,7 +33799,7 @@
       </c>
       <c r="O604" s="20"/>
     </row>
-    <row r="605" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A605" s="21" t="s">
         <v>1741</v>
       </c>
@@ -33834,7 +33842,7 @@
       <c r="N605" s="15"/>
       <c r="O605" s="22"/>
     </row>
-    <row r="606" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A606" s="19" t="s">
         <v>1749</v>
       </c>
@@ -33877,7 +33885,7 @@
       <c r="N606" s="13"/>
       <c r="O606" s="20"/>
     </row>
-    <row r="607" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A607" s="21" t="s">
         <v>1750</v>
       </c>
@@ -33922,7 +33930,7 @@
       </c>
       <c r="O607" s="22"/>
     </row>
-    <row r="608" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A608" s="19" t="s">
         <v>1752</v>
       </c>
@@ -33965,7 +33973,7 @@
       <c r="N608" s="13"/>
       <c r="O608" s="20"/>
     </row>
-    <row r="609" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A609" s="21" t="s">
         <v>1755</v>
       </c>
@@ -34010,7 +34018,7 @@
       </c>
       <c r="O609" s="22"/>
     </row>
-    <row r="610" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A610" s="19" t="s">
         <v>1756</v>
       </c>
@@ -34053,7 +34061,7 @@
       <c r="N610" s="13"/>
       <c r="O610" s="20"/>
     </row>
-    <row r="611" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A611" s="21" t="s">
         <v>1760</v>
       </c>
@@ -34096,7 +34104,7 @@
       <c r="N611" s="15"/>
       <c r="O611" s="22"/>
     </row>
-    <row r="612" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A612" s="19" t="s">
         <v>1765</v>
       </c>
@@ -34141,7 +34149,7 @@
       </c>
       <c r="O612" s="20"/>
     </row>
-    <row r="613" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A613" s="21" t="s">
         <v>1767</v>
       </c>
@@ -34186,7 +34194,7 @@
       </c>
       <c r="O613" s="22"/>
     </row>
-    <row r="614" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A614" s="19" t="s">
         <v>1769</v>
       </c>
@@ -34229,7 +34237,7 @@
       <c r="N614" s="13"/>
       <c r="O614" s="20"/>
     </row>
-    <row r="615" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A615" s="21" t="s">
         <v>1770</v>
       </c>
@@ -34274,7 +34282,7 @@
       </c>
       <c r="O615" s="22"/>
     </row>
-    <row r="616" spans="1:15" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:15" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A616" s="19" t="s">
         <v>1773</v>
       </c>
@@ -34317,7 +34325,7 @@
       <c r="N616" s="13"/>
       <c r="O616" s="20"/>
     </row>
-    <row r="617" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A617" s="21" t="s">
         <v>1775</v>
       </c>
@@ -34362,7 +34370,7 @@
       </c>
       <c r="O617" s="22"/>
     </row>
-    <row r="618" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A618" s="19" t="s">
         <v>1777</v>
       </c>
@@ -34405,7 +34413,7 @@
       <c r="N618" s="13"/>
       <c r="O618" s="20"/>
     </row>
-    <row r="619" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A619" s="21" t="s">
         <v>1778</v>
       </c>
@@ -34450,7 +34458,7 @@
       </c>
       <c r="O619" s="22"/>
     </row>
-    <row r="620" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A620" s="19" t="s">
         <v>1780</v>
       </c>
@@ -34493,7 +34501,7 @@
       <c r="N620" s="13"/>
       <c r="O620" s="20"/>
     </row>
-    <row r="621" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A621" s="21" t="s">
         <v>1787</v>
       </c>
@@ -34538,7 +34546,7 @@
       </c>
       <c r="O621" s="22"/>
     </row>
-    <row r="622" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A622" s="19" t="s">
         <v>1788</v>
       </c>
@@ -34581,7 +34589,7 @@
       <c r="N622" s="13"/>
       <c r="O622" s="20"/>
     </row>
-    <row r="623" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A623" s="21" t="s">
         <v>1791</v>
       </c>
@@ -34624,7 +34632,7 @@
       <c r="N623" s="15"/>
       <c r="O623" s="22"/>
     </row>
-    <row r="624" spans="1:15" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:15" ht="201.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A624" s="19" t="s">
         <v>1793</v>
       </c>
@@ -34667,7 +34675,7 @@
       <c r="N624" s="13"/>
       <c r="O624" s="20"/>
     </row>
-    <row r="625" spans="1:15" ht="259.2" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:15" ht="259.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A625" s="21" t="s">
         <v>1795</v>
       </c>
@@ -34712,7 +34720,7 @@
       </c>
       <c r="O625" s="22"/>
     </row>
-    <row r="626" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A626" s="19" t="s">
         <v>1797</v>
       </c>
@@ -34755,7 +34763,7 @@
       <c r="N626" s="13"/>
       <c r="O626" s="20"/>
     </row>
-    <row r="627" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A627" s="21" t="s">
         <v>1799</v>
       </c>
@@ -34800,7 +34808,7 @@
       </c>
       <c r="O627" s="22"/>
     </row>
-    <row r="628" spans="1:15" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:15" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A628" s="19" t="s">
         <v>1801</v>
       </c>
@@ -34843,7 +34851,7 @@
       <c r="N628" s="13"/>
       <c r="O628" s="20"/>
     </row>
-    <row r="629" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A629" s="21" t="s">
         <v>1803</v>
       </c>
@@ -34886,7 +34894,7 @@
       <c r="N629" s="15"/>
       <c r="O629" s="22"/>
     </row>
-    <row r="630" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A630" s="19" t="s">
         <v>1804</v>
       </c>
@@ -34931,7 +34939,7 @@
       </c>
       <c r="O630" s="20"/>
     </row>
-    <row r="631" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A631" s="21" t="s">
         <v>1806</v>
       </c>
@@ -34974,7 +34982,7 @@
       <c r="N631" s="15"/>
       <c r="O631" s="22"/>
     </row>
-    <row r="632" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A632" s="19" t="s">
         <v>1809</v>
       </c>
@@ -35019,7 +35027,7 @@
       </c>
       <c r="O632" s="20"/>
     </row>
-    <row r="633" spans="1:15" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:15" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A633" s="21" t="s">
         <v>1813</v>
       </c>
@@ -35062,7 +35070,7 @@
       <c r="N633" s="15"/>
       <c r="O633" s="22"/>
     </row>
-    <row r="634" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A634" s="19" t="s">
         <v>1820</v>
       </c>
@@ -35105,7 +35113,7 @@
       <c r="N634" s="13"/>
       <c r="O634" s="20"/>
     </row>
-    <row r="635" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A635" s="21" t="s">
         <v>1822</v>
       </c>
@@ -35148,7 +35156,7 @@
       <c r="N635" s="15"/>
       <c r="O635" s="22"/>
     </row>
-    <row r="636" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A636" s="19" t="s">
         <v>1824</v>
       </c>
@@ -35191,7 +35199,7 @@
       <c r="N636" s="13"/>
       <c r="O636" s="20"/>
     </row>
-    <row r="637" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A637" s="21" t="s">
         <v>1828</v>
       </c>
@@ -35236,7 +35244,7 @@
       </c>
       <c r="O637" s="22"/>
     </row>
-    <row r="638" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A638" s="19" t="s">
         <v>1829</v>
       </c>
@@ -35279,7 +35287,7 @@
       <c r="N638" s="13"/>
       <c r="O638" s="20"/>
     </row>
-    <row r="639" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A639" s="21" t="s">
         <v>1833</v>
       </c>
@@ -35322,7 +35330,7 @@
       <c r="N639" s="15"/>
       <c r="O639" s="22"/>
     </row>
-    <row r="640" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A640" s="19" t="s">
         <v>1838</v>
       </c>
@@ -35365,7 +35373,7 @@
       <c r="N640" s="13"/>
       <c r="O640" s="20"/>
     </row>
-    <row r="641" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A641" s="21" t="s">
         <v>1840</v>
       </c>
@@ -35408,7 +35416,7 @@
       <c r="N641" s="15"/>
       <c r="O641" s="22"/>
     </row>
-    <row r="642" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A642" s="19" t="s">
         <v>1842</v>
       </c>
@@ -35451,7 +35459,7 @@
       <c r="N642" s="13"/>
       <c r="O642" s="20"/>
     </row>
-    <row r="643" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A643" s="21" t="s">
         <v>1843</v>
       </c>
@@ -35494,7 +35502,7 @@
       <c r="N643" s="15"/>
       <c r="O643" s="22"/>
     </row>
-    <row r="644" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A644" s="19" t="s">
         <v>1845</v>
       </c>
@@ -35539,7 +35547,7 @@
       </c>
       <c r="O644" s="20"/>
     </row>
-    <row r="645" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A645" s="21" t="s">
         <v>1846</v>
       </c>
@@ -35584,7 +35592,7 @@
       </c>
       <c r="O645" s="22"/>
     </row>
-    <row r="646" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A646" s="19" t="s">
         <v>1848</v>
       </c>
@@ -35627,7 +35635,7 @@
       <c r="N646" s="13"/>
       <c r="O646" s="20"/>
     </row>
-    <row r="647" spans="1:15" ht="144" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:15" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A647" s="21" t="s">
         <v>1849</v>
       </c>
@@ -35670,7 +35678,7 @@
       <c r="N647" s="15"/>
       <c r="O647" s="22"/>
     </row>
-    <row r="648" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A648" s="19" t="s">
         <v>1850</v>
       </c>
@@ -35713,7 +35721,7 @@
       <c r="N648" s="13"/>
       <c r="O648" s="20"/>
     </row>
-    <row r="649" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A649" s="21" t="s">
         <v>1851</v>
       </c>
@@ -35758,7 +35766,7 @@
       </c>
       <c r="O649" s="22"/>
     </row>
-    <row r="650" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A650" s="19" t="s">
         <v>1853</v>
       </c>
@@ -35801,7 +35809,7 @@
       <c r="N650" s="13"/>
       <c r="O650" s="20"/>
     </row>
-    <row r="651" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A651" s="21" t="s">
         <v>1855</v>
       </c>
@@ -35846,7 +35854,7 @@
       </c>
       <c r="O651" s="22"/>
     </row>
-    <row r="652" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A652" s="19" t="s">
         <v>1857</v>
       </c>
@@ -35889,7 +35897,7 @@
       <c r="N652" s="13"/>
       <c r="O652" s="20"/>
     </row>
-    <row r="653" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A653" s="21" t="s">
         <v>1858</v>
       </c>
@@ -35932,7 +35940,7 @@
       <c r="N653" s="15"/>
       <c r="O653" s="22"/>
     </row>
-    <row r="654" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A654" s="19" t="s">
         <v>1862</v>
       </c>
@@ -35977,7 +35985,7 @@
       </c>
       <c r="O654" s="20"/>
     </row>
-    <row r="655" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A655" s="21" t="s">
         <v>1864</v>
       </c>
@@ -36020,7 +36028,7 @@
       <c r="N655" s="15"/>
       <c r="O655" s="22"/>
     </row>
-    <row r="656" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A656" s="19" t="s">
         <v>1865</v>
       </c>
@@ -36063,7 +36071,7 @@
       <c r="N656" s="13"/>
       <c r="O656" s="20"/>
     </row>
-    <row r="657" spans="1:15" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:15" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A657" s="21" t="s">
         <v>1867</v>
       </c>
@@ -36108,7 +36116,7 @@
       </c>
       <c r="O657" s="22"/>
     </row>
-    <row r="658" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A658" s="19" t="s">
         <v>1872</v>
       </c>
@@ -36151,7 +36159,7 @@
       <c r="N658" s="13"/>
       <c r="O658" s="20"/>
     </row>
-    <row r="659" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A659" s="21" t="s">
         <v>1873</v>
       </c>
@@ -36194,7 +36202,7 @@
       <c r="N659" s="15"/>
       <c r="O659" s="22"/>
     </row>
-    <row r="660" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A660" s="19" t="s">
         <v>1876</v>
       </c>
@@ -36239,7 +36247,7 @@
       </c>
       <c r="O660" s="20"/>
     </row>
-    <row r="661" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A661" s="21" t="s">
         <v>1878</v>
       </c>
@@ -36282,7 +36290,7 @@
       <c r="N661" s="15"/>
       <c r="O661" s="22"/>
     </row>
-    <row r="662" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A662" s="19" t="s">
         <v>1880</v>
       </c>
@@ -36325,7 +36333,7 @@
       <c r="N662" s="13"/>
       <c r="O662" s="20"/>
     </row>
-    <row r="663" spans="1:15" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:15" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A663" s="21" t="s">
         <v>1884</v>
       </c>
@@ -36368,7 +36376,7 @@
       <c r="N663" s="15"/>
       <c r="O663" s="22"/>
     </row>
-    <row r="664" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A664" s="19" t="s">
         <v>1885</v>
       </c>
@@ -36413,7 +36421,7 @@
       </c>
       <c r="O664" s="20"/>
     </row>
-    <row r="665" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A665" s="21" t="s">
         <v>1889</v>
       </c>
@@ -36456,7 +36464,7 @@
       <c r="N665" s="15"/>
       <c r="O665" s="22"/>
     </row>
-    <row r="666" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A666" s="19" t="s">
         <v>1890</v>
       </c>
@@ -36499,7 +36507,7 @@
       <c r="N666" s="13"/>
       <c r="O666" s="20"/>
     </row>
-    <row r="667" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A667" s="21" t="s">
         <v>1891</v>
       </c>
@@ -36542,7 +36550,7 @@
       <c r="N667" s="15"/>
       <c r="O667" s="22"/>
     </row>
-    <row r="668" spans="1:15" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:15" ht="316.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A668" s="19" t="s">
         <v>1894</v>
       </c>
@@ -36585,7 +36593,7 @@
       <c r="N668" s="13"/>
       <c r="O668" s="20"/>
     </row>
-    <row r="669" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A669" s="21" t="s">
         <v>1896</v>
       </c>
@@ -36628,7 +36636,7 @@
       <c r="N669" s="15"/>
       <c r="O669" s="22"/>
     </row>
-    <row r="670" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A670" s="19" t="s">
         <v>1901</v>
       </c>
@@ -36671,7 +36679,7 @@
       <c r="N670" s="13"/>
       <c r="O670" s="20"/>
     </row>
-    <row r="671" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A671" s="21" t="s">
         <v>1903</v>
       </c>
@@ -36714,7 +36722,7 @@
       <c r="N671" s="15"/>
       <c r="O671" s="22"/>
     </row>
-    <row r="672" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A672" s="19" t="s">
         <v>1905</v>
       </c>
@@ -36757,7 +36765,7 @@
       <c r="N672" s="13"/>
       <c r="O672" s="20"/>
     </row>
-    <row r="673" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A673" s="21" t="s">
         <v>1907</v>
       </c>
@@ -36800,7 +36808,7 @@
       <c r="N673" s="15"/>
       <c r="O673" s="22"/>
     </row>
-    <row r="674" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A674" s="19" t="s">
         <v>1912</v>
       </c>
@@ -36843,7 +36851,7 @@
       <c r="N674" s="13"/>
       <c r="O674" s="20"/>
     </row>
-    <row r="675" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A675" s="21" t="s">
         <v>1915</v>
       </c>
@@ -36886,7 +36894,7 @@
       <c r="N675" s="15"/>
       <c r="O675" s="22"/>
     </row>
-    <row r="676" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A676" s="19" t="s">
         <v>1919</v>
       </c>
@@ -36931,7 +36939,7 @@
       </c>
       <c r="O676" s="20"/>
     </row>
-    <row r="677" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A677" s="21" t="s">
         <v>1925</v>
       </c>
@@ -36974,7 +36982,7 @@
       <c r="N677" s="15"/>
       <c r="O677" s="22"/>
     </row>
-    <row r="678" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A678" s="19" t="s">
         <v>1926</v>
       </c>
@@ -37017,7 +37025,7 @@
       <c r="N678" s="13"/>
       <c r="O678" s="20"/>
     </row>
-    <row r="679" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A679" s="21" t="s">
         <v>1930</v>
       </c>
@@ -37060,7 +37068,7 @@
       <c r="N679" s="15"/>
       <c r="O679" s="22"/>
     </row>
-    <row r="680" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A680" s="19" t="s">
         <v>1931</v>
       </c>
@@ -37103,7 +37111,7 @@
       <c r="N680" s="13"/>
       <c r="O680" s="20"/>
     </row>
-    <row r="681" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A681" s="21" t="s">
         <v>1933</v>
       </c>
@@ -37148,7 +37156,7 @@
       </c>
       <c r="O681" s="22"/>
     </row>
-    <row r="682" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A682" s="19" t="s">
         <v>1936</v>
       </c>
@@ -37191,7 +37199,7 @@
       <c r="N682" s="13"/>
       <c r="O682" s="20"/>
     </row>
-    <row r="683" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A683" s="21" t="s">
         <v>1937</v>
       </c>
@@ -37234,7 +37242,7 @@
       <c r="N683" s="15"/>
       <c r="O683" s="22"/>
     </row>
-    <row r="684" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A684" s="19" t="s">
         <v>1939</v>
       </c>
@@ -37277,7 +37285,7 @@
       <c r="N684" s="13"/>
       <c r="O684" s="20"/>
     </row>
-    <row r="685" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A685" s="21" t="s">
         <v>1941</v>
       </c>
@@ -37322,7 +37330,7 @@
       </c>
       <c r="O685" s="22"/>
     </row>
-    <row r="686" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A686" s="19" t="s">
         <v>1943</v>
       </c>
@@ -37365,7 +37373,7 @@
       <c r="N686" s="13"/>
       <c r="O686" s="20"/>
     </row>
-    <row r="687" spans="1:15" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:15" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A687" s="21" t="s">
         <v>1944</v>
       </c>
@@ -37408,7 +37416,7 @@
       <c r="N687" s="15"/>
       <c r="O687" s="22"/>
     </row>
-    <row r="688" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A688" s="19" t="s">
         <v>1947</v>
       </c>
@@ -37451,7 +37459,7 @@
       <c r="N688" s="13"/>
       <c r="O688" s="20"/>
     </row>
-    <row r="689" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A689" s="21" t="s">
         <v>1953</v>
       </c>
@@ -37494,7 +37502,7 @@
       <c r="N689" s="15"/>
       <c r="O689" s="22"/>
     </row>
-    <row r="690" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A690" s="19" t="s">
         <v>1966</v>
       </c>
@@ -37537,7 +37545,7 @@
       <c r="N690" s="13"/>
       <c r="O690" s="20"/>
     </row>
-    <row r="691" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A691" s="21" t="s">
         <v>1967</v>
       </c>
@@ -37580,7 +37588,7 @@
       <c r="N691" s="15"/>
       <c r="O691" s="22"/>
     </row>
-    <row r="692" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A692" s="19" t="s">
         <v>1969</v>
       </c>
@@ -37625,7 +37633,7 @@
       </c>
       <c r="O692" s="20"/>
     </row>
-    <row r="693" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A693" s="21" t="s">
         <v>1972</v>
       </c>
@@ -37668,7 +37676,7 @@
       <c r="N693" s="15"/>
       <c r="O693" s="22"/>
     </row>
-    <row r="694" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A694" s="19" t="s">
         <v>1973</v>
       </c>
@@ -37711,7 +37719,7 @@
       <c r="N694" s="13"/>
       <c r="O694" s="20"/>
     </row>
-    <row r="695" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A695" s="21" t="s">
         <v>1976</v>
       </c>
@@ -37754,7 +37762,7 @@
       <c r="N695" s="15"/>
       <c r="O695" s="22"/>
     </row>
-    <row r="696" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A696" s="19" t="s">
         <v>1979</v>
       </c>
@@ -37797,7 +37805,7 @@
       <c r="N696" s="13"/>
       <c r="O696" s="20"/>
     </row>
-    <row r="697" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A697" s="21" t="s">
         <v>1985</v>
       </c>
@@ -37840,7 +37848,7 @@
       <c r="N697" s="15"/>
       <c r="O697" s="22"/>
     </row>
-    <row r="698" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A698" s="19" t="s">
         <v>1987</v>
       </c>
@@ -37883,7 +37891,7 @@
       <c r="N698" s="13"/>
       <c r="O698" s="20"/>
     </row>
-    <row r="699" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A699" s="21" t="s">
         <v>1989</v>
       </c>
@@ -37926,7 +37934,7 @@
       <c r="N699" s="15"/>
       <c r="O699" s="22"/>
     </row>
-    <row r="700" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A700" s="19" t="s">
         <v>1990</v>
       </c>
@@ -37971,7 +37979,7 @@
       </c>
       <c r="O700" s="20"/>
     </row>
-    <row r="701" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A701" s="21" t="s">
         <v>1992</v>
       </c>
@@ -38014,7 +38022,7 @@
       <c r="N701" s="15"/>
       <c r="O701" s="22"/>
     </row>
-    <row r="702" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A702" s="19" t="s">
         <v>1994</v>
       </c>
@@ -38059,7 +38067,7 @@
       </c>
       <c r="O702" s="20"/>
     </row>
-    <row r="703" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A703" s="21" t="s">
         <v>1996</v>
       </c>
@@ -38104,7 +38112,7 @@
       </c>
       <c r="O703" s="22"/>
     </row>
-    <row r="704" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A704" s="19" t="s">
         <v>1997</v>
       </c>
@@ -38147,7 +38155,7 @@
       <c r="N704" s="13"/>
       <c r="O704" s="20"/>
     </row>
-    <row r="705" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A705" s="21" t="s">
         <v>2001</v>
       </c>
@@ -38190,7 +38198,7 @@
       <c r="N705" s="15"/>
       <c r="O705" s="22"/>
     </row>
-    <row r="706" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A706" s="19" t="s">
         <v>2003</v>
       </c>
@@ -38235,7 +38243,7 @@
       </c>
       <c r="O706" s="20"/>
     </row>
-    <row r="707" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A707" s="21" t="s">
         <v>2014</v>
       </c>
@@ -38280,7 +38288,7 @@
       </c>
       <c r="O707" s="22"/>
     </row>
-    <row r="708" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A708" s="19" t="s">
         <v>2016</v>
       </c>
@@ -38325,7 +38333,7 @@
       </c>
       <c r="O708" s="20"/>
     </row>
-    <row r="709" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A709" s="21" t="s">
         <v>2017</v>
       </c>
@@ -38368,7 +38376,7 @@
       <c r="N709" s="15"/>
       <c r="O709" s="22"/>
     </row>
-    <row r="710" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A710" s="19" t="s">
         <v>2019</v>
       </c>
@@ -38411,7 +38419,7 @@
       <c r="N710" s="13"/>
       <c r="O710" s="20"/>
     </row>
-    <row r="711" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A711" s="21" t="s">
         <v>2023</v>
       </c>
@@ -38454,7 +38462,7 @@
       <c r="N711" s="15"/>
       <c r="O711" s="22"/>
     </row>
-    <row r="712" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A712" s="19" t="s">
         <v>2025</v>
       </c>
@@ -38499,7 +38507,7 @@
       </c>
       <c r="O712" s="20"/>
     </row>
-    <row r="713" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A713" s="21" t="s">
         <v>2026</v>
       </c>
@@ -38542,7 +38550,7 @@
       <c r="N713" s="15"/>
       <c r="O713" s="22"/>
     </row>
-    <row r="714" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A714" s="19" t="s">
         <v>2029</v>
       </c>
@@ -38585,7 +38593,7 @@
       <c r="N714" s="13"/>
       <c r="O714" s="20"/>
     </row>
-    <row r="715" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A715" s="21" t="s">
         <v>2030</v>
       </c>
@@ -38628,7 +38636,7 @@
       <c r="N715" s="15"/>
       <c r="O715" s="22"/>
     </row>
-    <row r="716" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A716" s="19" t="s">
         <v>2032</v>
       </c>
@@ -38671,7 +38679,7 @@
       <c r="N716" s="13"/>
       <c r="O716" s="20"/>
     </row>
-    <row r="717" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A717" s="21" t="s">
         <v>2035</v>
       </c>
@@ -38714,7 +38722,7 @@
       <c r="N717" s="15"/>
       <c r="O717" s="22"/>
     </row>
-    <row r="718" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A718" s="19" t="s">
         <v>2038</v>
       </c>
@@ -38757,7 +38765,7 @@
       <c r="N718" s="13"/>
       <c r="O718" s="20"/>
     </row>
-    <row r="719" spans="1:15" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:15" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A719" s="21" t="s">
         <v>2043</v>
       </c>
@@ -38800,7 +38808,7 @@
       <c r="N719" s="15"/>
       <c r="O719" s="22"/>
     </row>
-    <row r="720" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A720" s="19" t="s">
         <v>2051</v>
       </c>
@@ -38845,7 +38853,7 @@
       </c>
       <c r="O720" s="20"/>
     </row>
-    <row r="721" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A721" s="21" t="s">
         <v>2053</v>
       </c>
@@ -38888,7 +38896,7 @@
       <c r="N721" s="15"/>
       <c r="O721" s="22"/>
     </row>
-    <row r="722" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A722" s="19" t="s">
         <v>2055</v>
       </c>
@@ -38931,7 +38939,7 @@
       <c r="N722" s="13"/>
       <c r="O722" s="20"/>
     </row>
-    <row r="723" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A723" s="21" t="s">
         <v>2056</v>
       </c>
@@ -38974,7 +38982,7 @@
       <c r="N723" s="15"/>
       <c r="O723" s="22"/>
     </row>
-    <row r="724" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A724" s="19" t="s">
         <v>2059</v>
       </c>
@@ -39017,7 +39025,7 @@
       <c r="N724" s="13"/>
       <c r="O724" s="20"/>
     </row>
-    <row r="725" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A725" s="21" t="s">
         <v>2061</v>
       </c>
@@ -39060,7 +39068,7 @@
       <c r="N725" s="15"/>
       <c r="O725" s="22"/>
     </row>
-    <row r="726" spans="1:15" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:15" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A726" s="19" t="s">
         <v>2063</v>
       </c>
@@ -39103,7 +39111,7 @@
       <c r="N726" s="13"/>
       <c r="O726" s="20"/>
     </row>
-    <row r="727" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A727" s="21" t="s">
         <v>2065</v>
       </c>
@@ -39146,7 +39154,7 @@
       <c r="N727" s="15"/>
       <c r="O727" s="22"/>
     </row>
-    <row r="728" spans="1:15" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:15" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A728" s="19" t="s">
         <v>2067</v>
       </c>
@@ -39189,7 +39197,7 @@
       <c r="N728" s="13"/>
       <c r="O728" s="20"/>
     </row>
-    <row r="729" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A729" s="21" t="s">
         <v>2069</v>
       </c>
@@ -39232,7 +39240,7 @@
       <c r="N729" s="15"/>
       <c r="O729" s="22"/>
     </row>
-    <row r="730" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A730" s="19" t="s">
         <v>2071</v>
       </c>
@@ -39275,7 +39283,7 @@
       <c r="N730" s="13"/>
       <c r="O730" s="20"/>
     </row>
-    <row r="731" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A731" s="21" t="s">
         <v>2072</v>
       </c>
@@ -39320,7 +39328,7 @@
       </c>
       <c r="O731" s="22"/>
     </row>
-    <row r="732" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A732" s="19" t="s">
         <v>2074</v>
       </c>
@@ -39363,7 +39371,7 @@
       <c r="N732" s="13"/>
       <c r="O732" s="20"/>
     </row>
-    <row r="733" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A733" s="21" t="s">
         <v>2078</v>
       </c>
@@ -39406,7 +39414,7 @@
       <c r="N733" s="15"/>
       <c r="O733" s="22"/>
     </row>
-    <row r="734" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A734" s="19" t="s">
         <v>2080</v>
       </c>
@@ -39449,7 +39457,7 @@
       <c r="N734" s="13"/>
       <c r="O734" s="20"/>
     </row>
-    <row r="735" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A735" s="21" t="s">
         <v>2083</v>
       </c>
@@ -39492,7 +39500,7 @@
       <c r="N735" s="15"/>
       <c r="O735" s="22"/>
     </row>
-    <row r="736" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A736" s="19" t="s">
         <v>2085</v>
       </c>
@@ -39535,7 +39543,7 @@
       <c r="N736" s="13"/>
       <c r="O736" s="20"/>
     </row>
-    <row r="737" spans="1:15" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:15" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A737" s="21" t="s">
         <v>2087</v>
       </c>
@@ -39580,7 +39588,7 @@
       </c>
       <c r="O737" s="22"/>
     </row>
-    <row r="738" spans="1:15" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:15" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A738" s="19" t="s">
         <v>2089</v>
       </c>
@@ -39623,7 +39631,7 @@
       <c r="N738" s="13"/>
       <c r="O738" s="20"/>
     </row>
-    <row r="739" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A739" s="21" t="s">
         <v>2091</v>
       </c>
@@ -39666,7 +39674,7 @@
       <c r="N739" s="15"/>
       <c r="O739" s="22"/>
     </row>
-    <row r="740" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A740" s="19" t="s">
         <v>2092</v>
       </c>
@@ -39709,7 +39717,7 @@
       <c r="N740" s="13"/>
       <c r="O740" s="20"/>
     </row>
-    <row r="741" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A741" s="21" t="s">
         <v>2096</v>
       </c>
@@ -39752,7 +39760,7 @@
       <c r="N741" s="15"/>
       <c r="O741" s="22"/>
     </row>
-    <row r="742" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A742" s="19" t="s">
         <v>2099</v>
       </c>
@@ -39795,7 +39803,7 @@
       <c r="N742" s="13"/>
       <c r="O742" s="20"/>
     </row>
-    <row r="743" spans="1:15" ht="403.2" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:15" ht="403.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A743" s="21" t="s">
         <v>2104</v>
       </c>
@@ -39840,7 +39848,7 @@
       </c>
       <c r="O743" s="22"/>
     </row>
-    <row r="744" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A744" s="19" t="s">
         <v>2106</v>
       </c>
@@ -39885,7 +39893,7 @@
       </c>
       <c r="O744" s="20"/>
     </row>
-    <row r="745" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A745" s="21" t="s">
         <v>2111</v>
       </c>
@@ -39928,7 +39936,7 @@
       <c r="N745" s="15"/>
       <c r="O745" s="22"/>
     </row>
-    <row r="746" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A746" s="19" t="s">
         <v>2114</v>
       </c>
@@ -39973,7 +39981,7 @@
       </c>
       <c r="O746" s="20"/>
     </row>
-    <row r="747" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A747" s="21" t="s">
         <v>2115</v>
       </c>
@@ -40016,7 +40024,7 @@
       <c r="N747" s="15"/>
       <c r="O747" s="22"/>
     </row>
-    <row r="748" spans="1:15" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:15" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A748" s="19" t="s">
         <v>2116</v>
       </c>
@@ -40059,7 +40067,7 @@
       <c r="N748" s="13"/>
       <c r="O748" s="20"/>
     </row>
-    <row r="749" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A749" s="21" t="s">
         <v>2118</v>
       </c>
@@ -40102,7 +40110,7 @@
       <c r="N749" s="15"/>
       <c r="O749" s="22"/>
     </row>
-    <row r="750" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A750" s="19" t="s">
         <v>2120</v>
       </c>
@@ -40145,7 +40153,7 @@
       <c r="N750" s="13"/>
       <c r="O750" s="20"/>
     </row>
-    <row r="751" spans="1:15" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:15" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A751" s="21" t="s">
         <v>2121</v>
       </c>
@@ -40188,7 +40196,7 @@
       <c r="N751" s="15"/>
       <c r="O751" s="22"/>
     </row>
-    <row r="752" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A752" s="19" t="s">
         <v>2123</v>
       </c>
@@ -40231,7 +40239,7 @@
       <c r="N752" s="13"/>
       <c r="O752" s="20"/>
     </row>
-    <row r="753" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A753" s="21" t="s">
         <v>2125</v>
       </c>
@@ -40274,7 +40282,7 @@
       <c r="N753" s="15"/>
       <c r="O753" s="22"/>
     </row>
-    <row r="754" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A754" s="19" t="s">
         <v>2126</v>
       </c>
@@ -40317,7 +40325,7 @@
       <c r="N754" s="13"/>
       <c r="O754" s="20"/>
     </row>
-    <row r="755" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A755" s="21" t="s">
         <v>2127</v>
       </c>
@@ -40360,7 +40368,7 @@
       <c r="N755" s="15"/>
       <c r="O755" s="22"/>
     </row>
-    <row r="756" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A756" s="19" t="s">
         <v>2131</v>
       </c>
@@ -40405,7 +40413,7 @@
       </c>
       <c r="O756" s="20"/>
     </row>
-    <row r="757" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A757" s="21" t="s">
         <v>2132</v>
       </c>
@@ -40450,7 +40458,7 @@
       </c>
       <c r="O757" s="22"/>
     </row>
-    <row r="758" spans="1:15" ht="144" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:15" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A758" s="19" t="s">
         <v>2133</v>
       </c>
@@ -40493,7 +40501,7 @@
       <c r="N758" s="13"/>
       <c r="O758" s="20"/>
     </row>
-    <row r="759" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A759" s="21" t="s">
         <v>2135</v>
       </c>
@@ -40538,7 +40546,7 @@
       </c>
       <c r="O759" s="22"/>
     </row>
-    <row r="760" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A760" s="19" t="s">
         <v>2141</v>
       </c>
@@ -40581,7 +40589,7 @@
       <c r="N760" s="13"/>
       <c r="O760" s="20"/>
     </row>
-    <row r="761" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A761" s="21" t="s">
         <v>2151</v>
       </c>
@@ -40624,7 +40632,7 @@
       <c r="N761" s="15"/>
       <c r="O761" s="22"/>
     </row>
-    <row r="762" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A762" s="19" t="s">
         <v>2154</v>
       </c>
@@ -40669,7 +40677,7 @@
       </c>
       <c r="O762" s="20"/>
     </row>
-    <row r="763" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A763" s="21" t="s">
         <v>2156</v>
       </c>
@@ -40714,7 +40722,7 @@
       </c>
       <c r="O763" s="22"/>
     </row>
-    <row r="764" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A764" s="19" t="s">
         <v>2157</v>
       </c>
@@ -40757,7 +40765,7 @@
       <c r="N764" s="13"/>
       <c r="O764" s="20"/>
     </row>
-    <row r="765" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A765" s="21" t="s">
         <v>2158</v>
       </c>
@@ -40802,7 +40810,7 @@
       </c>
       <c r="O765" s="22"/>
     </row>
-    <row r="766" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A766" s="19" t="s">
         <v>2160</v>
       </c>
@@ -40845,7 +40853,7 @@
       <c r="N766" s="13"/>
       <c r="O766" s="20"/>
     </row>
-    <row r="767" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A767" s="21" t="s">
         <v>2161</v>
       </c>
@@ -40890,7 +40898,7 @@
       </c>
       <c r="O767" s="22"/>
     </row>
-    <row r="768" spans="1:15" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:15" ht="201.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A768" s="19" t="s">
         <v>2166</v>
       </c>
@@ -40935,7 +40943,7 @@
       </c>
       <c r="O768" s="20"/>
     </row>
-    <row r="769" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A769" s="21" t="s">
         <v>2167</v>
       </c>
@@ -40978,7 +40986,7 @@
       <c r="N769" s="15"/>
       <c r="O769" s="22"/>
     </row>
-    <row r="770" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A770" s="19" t="s">
         <v>2168</v>
       </c>
@@ -41021,7 +41029,7 @@
       <c r="N770" s="13"/>
       <c r="O770" s="20"/>
     </row>
-    <row r="771" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A771" s="21" t="s">
         <v>2172</v>
       </c>
@@ -41064,7 +41072,7 @@
       <c r="N771" s="15"/>
       <c r="O771" s="22"/>
     </row>
-    <row r="772" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A772" s="19" t="s">
         <v>2173</v>
       </c>
@@ -41107,7 +41115,7 @@
       <c r="N772" s="13"/>
       <c r="O772" s="20"/>
     </row>
-    <row r="773" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A773" s="21" t="s">
         <v>2181</v>
       </c>
@@ -41152,7 +41160,7 @@
       </c>
       <c r="O773" s="22"/>
     </row>
-    <row r="774" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A774" s="19" t="s">
         <v>2183</v>
       </c>
@@ -41195,7 +41203,7 @@
       <c r="N774" s="13"/>
       <c r="O774" s="20"/>
     </row>
-    <row r="775" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A775" s="21" t="s">
         <v>2185</v>
       </c>
@@ -41240,7 +41248,7 @@
       </c>
       <c r="O775" s="22"/>
     </row>
-    <row r="776" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A776" s="19" t="s">
         <v>2187</v>
       </c>
@@ -41285,7 +41293,7 @@
       </c>
       <c r="O776" s="20"/>
     </row>
-    <row r="777" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A777" s="21" t="s">
         <v>2191</v>
       </c>
@@ -41328,7 +41336,7 @@
       <c r="N777" s="15"/>
       <c r="O777" s="22"/>
     </row>
-    <row r="778" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A778" s="19" t="s">
         <v>2192</v>
       </c>
@@ -41371,7 +41379,7 @@
       <c r="N778" s="13"/>
       <c r="O778" s="20"/>
     </row>
-    <row r="779" spans="1:15" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:15" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A779" s="21" t="s">
         <v>2193</v>
       </c>
@@ -41416,7 +41424,7 @@
       </c>
       <c r="O779" s="22"/>
     </row>
-    <row r="780" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A780" s="19" t="s">
         <v>2196</v>
       </c>
@@ -41459,7 +41467,7 @@
       <c r="N780" s="13"/>
       <c r="O780" s="20"/>
     </row>
-    <row r="781" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A781" s="21" t="s">
         <v>2200</v>
       </c>
@@ -41502,7 +41510,7 @@
       <c r="N781" s="15"/>
       <c r="O781" s="22"/>
     </row>
-    <row r="782" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A782" s="19" t="s">
         <v>2202</v>
       </c>
@@ -41545,7 +41553,7 @@
       <c r="N782" s="13"/>
       <c r="O782" s="20"/>
     </row>
-    <row r="783" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A783" s="21" t="s">
         <v>2203</v>
       </c>
@@ -41590,7 +41598,7 @@
       </c>
       <c r="O783" s="22"/>
     </row>
-    <row r="784" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A784" s="19" t="s">
         <v>2205</v>
       </c>
@@ -41633,7 +41641,7 @@
       <c r="N784" s="13"/>
       <c r="O784" s="20"/>
     </row>
-    <row r="785" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A785" s="21" t="s">
         <v>2207</v>
       </c>
@@ -41676,7 +41684,7 @@
       <c r="N785" s="15"/>
       <c r="O785" s="22"/>
     </row>
-    <row r="786" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:15" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A786" s="19" t="s">
         <v>2208</v>
       </c>
@@ -41721,7 +41729,7 @@
       </c>
       <c r="O786" s="20"/>
     </row>
-    <row r="787" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A787" s="21" t="s">
         <v>2211</v>
       </c>
@@ -41764,7 +41772,7 @@
       <c r="N787" s="15"/>
       <c r="O787" s="22"/>
     </row>
-    <row r="788" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A788" s="19" t="s">
         <v>2212</v>
       </c>
@@ -41807,7 +41815,7 @@
       <c r="N788" s="13"/>
       <c r="O788" s="20"/>
     </row>
-    <row r="789" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="789" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A789" s="21" t="s">
         <v>2214</v>
       </c>
@@ -41850,7 +41858,7 @@
       <c r="N789" s="15"/>
       <c r="O789" s="22"/>
     </row>
-    <row r="790" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A790" s="19" t="s">
         <v>2215</v>
       </c>
@@ -41893,7 +41901,7 @@
       <c r="N790" s="13"/>
       <c r="O790" s="20"/>
     </row>
-    <row r="791" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A791" s="21" t="s">
         <v>2218</v>
       </c>
@@ -41936,7 +41944,7 @@
       <c r="N791" s="15"/>
       <c r="O791" s="22"/>
     </row>
-    <row r="792" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="792" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A792" s="19" t="s">
         <v>2220</v>
       </c>
@@ -41979,7 +41987,7 @@
       <c r="N792" s="13"/>
       <c r="O792" s="20"/>
     </row>
-    <row r="793" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A793" s="21" t="s">
         <v>2227</v>
       </c>
@@ -42022,7 +42030,7 @@
       <c r="N793" s="15"/>
       <c r="O793" s="22"/>
     </row>
-    <row r="794" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A794" s="19" t="s">
         <v>2228</v>
       </c>
@@ -42065,7 +42073,7 @@
       <c r="N794" s="13"/>
       <c r="O794" s="20"/>
     </row>
-    <row r="795" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A795" s="21" t="s">
         <v>2229</v>
       </c>
@@ -42110,7 +42118,7 @@
       </c>
       <c r="O795" s="22"/>
     </row>
-    <row r="796" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="796" spans="1:15" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A796" s="19" t="s">
         <v>2232</v>
       </c>
@@ -42153,7 +42161,7 @@
       <c r="N796" s="13"/>
       <c r="O796" s="20"/>
     </row>
-    <row r="797" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A797" s="21" t="s">
         <v>2234</v>
       </c>
@@ -42196,7 +42204,7 @@
       <c r="N797" s="15"/>
       <c r="O797" s="22"/>
     </row>
-    <row r="798" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="798" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A798" s="19" t="s">
         <v>2236</v>
       </c>
@@ -42239,7 +42247,7 @@
       <c r="N798" s="13"/>
       <c r="O798" s="20"/>
     </row>
-    <row r="799" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="799" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A799" s="21" t="s">
         <v>2238</v>
       </c>
@@ -42282,7 +42290,7 @@
       <c r="N799" s="15"/>
       <c r="O799" s="22"/>
     </row>
-    <row r="800" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A800" s="19" t="s">
         <v>2242</v>
       </c>
@@ -42327,7 +42335,7 @@
       </c>
       <c r="O800" s="20"/>
     </row>
-    <row r="801" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A801" s="21" t="s">
         <v>2243</v>
       </c>
@@ -42370,7 +42378,7 @@
       <c r="N801" s="15"/>
       <c r="O801" s="22"/>
     </row>
-    <row r="802" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A802" s="19" t="s">
         <v>2244</v>
       </c>
@@ -42413,7 +42421,7 @@
       <c r="N802" s="13"/>
       <c r="O802" s="20"/>
     </row>
-    <row r="803" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A803" s="21" t="s">
         <v>2247</v>
       </c>
@@ -42456,7 +42464,7 @@
       <c r="N803" s="15"/>
       <c r="O803" s="22"/>
     </row>
-    <row r="804" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A804" s="19" t="s">
         <v>2251</v>
       </c>
@@ -42499,7 +42507,7 @@
       <c r="N804" s="13"/>
       <c r="O804" s="20"/>
     </row>
-    <row r="805" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:15" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A805" s="21" t="s">
         <v>2255</v>
       </c>
@@ -42544,7 +42552,7 @@
       </c>
       <c r="O805" s="22"/>
     </row>
-    <row r="806" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="806" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A806" s="19" t="s">
         <v>2259</v>
       </c>
@@ -42589,7 +42597,7 @@
       </c>
       <c r="O806" s="20"/>
     </row>
-    <row r="807" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:15" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A807" s="21" t="s">
         <v>2261</v>
       </c>
@@ -42632,7 +42640,7 @@
       <c r="N807" s="15"/>
       <c r="O807" s="22"/>
     </row>
-    <row r="808" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="808" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A808" s="19" t="s">
         <v>2263</v>
       </c>
@@ -42675,7 +42683,7 @@
       <c r="N808" s="13"/>
       <c r="O808" s="20"/>
     </row>
-    <row r="809" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="809" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A809" s="21" t="s">
         <v>2265</v>
       </c>
@@ -42720,7 +42728,7 @@
       </c>
       <c r="O809" s="22"/>
     </row>
-    <row r="810" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A810" s="19" t="s">
         <v>2267</v>
       </c>
@@ -42763,7 +42771,7 @@
       <c r="N810" s="13"/>
       <c r="O810" s="20"/>
     </row>
-    <row r="811" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:15" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A811" s="21" t="s">
         <v>2271</v>
       </c>
@@ -42806,7 +42814,7 @@
       <c r="N811" s="15"/>
       <c r="O811" s="22"/>
     </row>
-    <row r="812" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="812" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A812" s="23" t="s">
         <v>2275</v>
       </c>
@@ -42850,6 +42858,16 @@
       <c r="O812" s="26"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:O812" xr:uid="{FDE07E1A-985C-40A8-94C0-CAAB4BA87E43}">
+    <filterColumn colId="12">
+      <filters>
+        <filter val="Disagree"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="13">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M1:M812" xr:uid="{65D351DC-7052-412E-8247-95CAB0D24D80}">
       <formula1>"Agree, Disagree"</formula1>
